--- a/gsc-export-old/Coverage.xlsx
+++ b/gsc-export-old/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="111">
   <si>
     <t>Date</t>
   </si>
@@ -29,18 +29,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-11-23</t>
+    <t>2025-11-25</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2025-11-24</t>
-  </si>
-  <si>
-    <t>2025-11-25</t>
-  </si>
-  <si>
     <t>2025-11-26</t>
   </si>
   <si>
@@ -291,6 +285,18 @@
   </si>
   <si>
     <t>2026-02-17</t>
+  </si>
+  <si>
+    <t>2026-02-18</t>
+  </si>
+  <si>
+    <t>2026-02-19</t>
+  </si>
+  <si>
+    <t>2026-02-20</t>
+  </si>
+  <si>
+    <t>2026-02-21</t>
   </si>
   <si>
     <t>Reason</t>
@@ -391,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -419,7 +425,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>9.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="3">
@@ -433,7 +439,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="4">
@@ -447,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="5">
@@ -461,7 +467,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="6">
@@ -475,7 +481,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="7">
@@ -489,7 +495,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="8">
@@ -503,7 +509,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +523,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="10">
@@ -531,7 +537,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="11">
@@ -545,7 +551,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="12">
@@ -559,7 +565,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="13">
@@ -573,7 +579,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="14">
@@ -587,7 +593,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="15">
@@ -601,7 +607,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="16">
@@ -615,7 +621,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="17">
@@ -629,7 +635,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="18">
@@ -657,7 +663,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="20">
@@ -671,7 +677,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="21">
@@ -685,35 +691,35 @@
         <v>5</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>3.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="B22" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C22" t="s" s="0">
-        <v>5</v>
+      <c r="B22" t="n" s="0">
+        <v>73.0</v>
+      </c>
+      <c r="C22" t="n" s="0">
+        <v>62.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="B23" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C23" t="s" s="0">
-        <v>5</v>
+      <c r="B23" t="n" s="0">
+        <v>79.0</v>
+      </c>
+      <c r="C23" t="n" s="0">
+        <v>56.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>16.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="24">
@@ -721,13 +727,13 @@
         <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>73.0</v>
+        <v>79.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>62.0</v>
+        <v>56.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="25">
@@ -741,7 +747,7 @@
         <v>56.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>9.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="26">
@@ -755,7 +761,7 @@
         <v>56.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="27">
@@ -769,7 +775,7 @@
         <v>56.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>15.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="28">
@@ -783,7 +789,7 @@
         <v>56.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="29">
@@ -797,7 +803,7 @@
         <v>56.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>7.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="30">
@@ -811,7 +817,7 @@
         <v>56.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="31">
@@ -819,13 +825,13 @@
         <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>79.0</v>
+        <v>85.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>56.0</v>
+        <v>50.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="32">
@@ -833,13 +839,13 @@
         <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>79.0</v>
+        <v>85.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>56.0</v>
+        <v>50.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="33">
@@ -853,7 +859,7 @@
         <v>50.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="34">
@@ -867,7 +873,7 @@
         <v>50.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="35">
@@ -895,7 +901,7 @@
         <v>50.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="37">
@@ -909,7 +915,7 @@
         <v>50.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="38">
@@ -923,7 +929,7 @@
         <v>50.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>0.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="39">
@@ -951,7 +957,7 @@
         <v>50.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>72.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="41">
@@ -965,7 +971,7 @@
         <v>50.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>1.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="42">
@@ -973,13 +979,13 @@
         <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>85.0</v>
+        <v>90.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>50.0</v>
+        <v>45.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="43">
@@ -987,13 +993,13 @@
         <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>85.0</v>
+        <v>90.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>50.0</v>
+        <v>45.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>29.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="44">
@@ -1007,7 +1013,7 @@
         <v>45.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>10.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="45">
@@ -1015,13 +1021,13 @@
         <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>90.0</v>
+        <v>93.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>45.0</v>
+        <v>42.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>2.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="46">
@@ -1029,13 +1035,13 @@
         <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>90.0</v>
+        <v>93.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>45.0</v>
+        <v>42.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>29.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="47">
@@ -1049,7 +1055,7 @@
         <v>42.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>40.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="48">
@@ -1063,7 +1069,7 @@
         <v>42.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>14.0</v>
+        <v>121.0</v>
       </c>
     </row>
     <row r="49">
@@ -1071,13 +1077,13 @@
         <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>42.0</v>
+        <v>41.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>85.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="50">
@@ -1085,13 +1091,13 @@
         <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>42.0</v>
+        <v>41.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>121.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="51">
@@ -1105,7 +1111,7 @@
         <v>41.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>9.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="52">
@@ -1113,13 +1119,13 @@
         <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>94.0</v>
+        <v>95.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>41.0</v>
+        <v>40.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>26.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="53">
@@ -1127,13 +1133,13 @@
         <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>94.0</v>
+        <v>95.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>41.0</v>
+        <v>40.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>67.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="54">
@@ -1147,7 +1153,7 @@
         <v>40.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>54.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="55">
@@ -1161,7 +1167,7 @@
         <v>40.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>25.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="56">
@@ -1169,13 +1175,13 @@
         <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>95.0</v>
+        <v>101.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>40.0</v>
+        <v>34.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>23.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="57">
@@ -1183,13 +1189,13 @@
         <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>95.0</v>
+        <v>101.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>40.0</v>
+        <v>34.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>33.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="58">
@@ -1203,7 +1209,7 @@
         <v>34.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>3.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="59">
@@ -1217,7 +1223,7 @@
         <v>34.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="60">
@@ -1231,7 +1237,7 @@
         <v>34.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>44.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="61">
@@ -1245,7 +1251,7 @@
         <v>34.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="62">
@@ -1259,7 +1265,7 @@
         <v>34.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>0.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="63">
@@ -1267,13 +1273,13 @@
         <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>101.0</v>
+        <v>104.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>34.0</v>
+        <v>31.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="64">
@@ -1281,13 +1287,13 @@
         <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>101.0</v>
+        <v>104.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>34.0</v>
+        <v>31.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>58.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="65">
@@ -1301,7 +1307,7 @@
         <v>31.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="66">
@@ -1309,13 +1315,13 @@
         <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>104.0</v>
+        <v>106.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="67">
@@ -1323,13 +1329,13 @@
         <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>104.0</v>
+        <v>106.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="68">
@@ -1343,7 +1349,7 @@
         <v>29.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="69">
@@ -1357,7 +1363,7 @@
         <v>29.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="70">
@@ -1365,13 +1371,13 @@
         <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>106.0</v>
+        <v>110.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>29.0</v>
+        <v>25.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="71">
@@ -1379,10 +1385,10 @@
         <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>106.0</v>
+        <v>110.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>29.0</v>
+        <v>25.0</v>
       </c>
       <c r="D71" t="n" s="0">
         <v>0.0</v>
@@ -1407,13 +1413,13 @@
         <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>110.0</v>
+        <v>114.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>25.0</v>
+        <v>21.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="74">
@@ -1421,13 +1427,13 @@
         <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>110.0</v>
+        <v>114.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>25.0</v>
+        <v>21.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="75">
@@ -1441,7 +1447,7 @@
         <v>21.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="76">
@@ -1455,7 +1461,7 @@
         <v>21.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="77">
@@ -1463,13 +1469,13 @@
         <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>114.0</v>
+        <v>121.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>21.0</v>
+        <v>14.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="78">
@@ -1477,10 +1483,10 @@
         <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>114.0</v>
+        <v>121.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>21.0</v>
+        <v>14.0</v>
       </c>
       <c r="D78" t="n" s="0">
         <v>0.0</v>
@@ -1497,7 +1503,7 @@
         <v>14.0</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="80">
@@ -1505,13 +1511,13 @@
         <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>121.0</v>
+        <v>135.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="81">
@@ -1519,10 +1525,10 @@
         <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>121.0</v>
+        <v>135.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="D81" t="n" s="0">
         <v>0.0</v>
@@ -1539,7 +1545,7 @@
         <v>0.0</v>
       </c>
       <c r="D82" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="83">
@@ -1624,6 +1630,34 @@
       </c>
       <c r="D88" t="n" s="0">
         <v>0.0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B89" t="n" s="0">
+        <v>135.0</v>
+      </c>
+      <c r="C89" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D89" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B90" t="n" s="0">
+        <v>135.0</v>
+      </c>
+      <c r="C90" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D90" t="s" s="0">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1638,41 +1672,41 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>103.0</v>
+        <v>104.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>99</v>
       </c>
-      <c r="B3" t="s" s="0">
-        <v>97</v>
-      </c>
       <c r="C3" t="s" s="0">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>4.0</v>
@@ -1680,13 +1714,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="C4" t="s" s="0">
         <v>100</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>97</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>98</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>3.0</v>
@@ -1694,13 +1728,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>15.0</v>
@@ -1708,16 +1742,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
     </row>
   </sheetData>
@@ -1732,16 +1766,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1756,18 +1790,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export-old/Coverage.xlsx
+++ b/gsc-export-old/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="109">
   <si>
     <t>Date</t>
   </si>
@@ -29,16 +29,10 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-11-25</t>
+    <t>2025-11-27</t>
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>2025-11-26</t>
-  </si>
-  <si>
-    <t>2025-11-27</t>
   </si>
   <si>
     <t>2025-11-28</t>
@@ -397,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -425,7 +419,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="3">
@@ -439,7 +433,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="4">
@@ -453,7 +447,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="5">
@@ -467,7 +461,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="6">
@@ -481,7 +475,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="7">
@@ -495,7 +489,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="8">
@@ -509,7 +503,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="9">
@@ -523,7 +517,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="10">
@@ -537,7 +531,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="11">
@@ -551,7 +545,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="12">
@@ -565,7 +559,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="13">
@@ -579,7 +573,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="14">
@@ -593,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="15">
@@ -607,7 +601,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="16">
@@ -635,7 +629,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="18">
@@ -649,7 +643,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="19">
@@ -663,35 +657,35 @@
         <v>5</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>3.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="B20" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C20" t="s" s="0">
-        <v>5</v>
+      <c r="B20" t="n" s="0">
+        <v>73.0</v>
+      </c>
+      <c r="C20" t="n" s="0">
+        <v>62.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B21" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C21" t="s" s="0">
-        <v>5</v>
+      <c r="B21" t="n" s="0">
+        <v>79.0</v>
+      </c>
+      <c r="C21" t="n" s="0">
+        <v>56.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>16.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="22">
@@ -699,13 +693,13 @@
         <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>73.0</v>
+        <v>79.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>62.0</v>
+        <v>56.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="23">
@@ -719,7 +713,7 @@
         <v>56.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>9.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="24">
@@ -733,7 +727,7 @@
         <v>56.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="25">
@@ -747,7 +741,7 @@
         <v>56.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>15.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="26">
@@ -761,7 +755,7 @@
         <v>56.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="27">
@@ -775,7 +769,7 @@
         <v>56.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>7.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="28">
@@ -789,7 +783,7 @@
         <v>56.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="29">
@@ -797,13 +791,13 @@
         <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>79.0</v>
+        <v>85.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>56.0</v>
+        <v>50.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="30">
@@ -811,13 +805,13 @@
         <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>79.0</v>
+        <v>85.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>56.0</v>
+        <v>50.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="31">
@@ -831,7 +825,7 @@
         <v>50.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="32">
@@ -845,7 +839,7 @@
         <v>50.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="33">
@@ -873,7 +867,7 @@
         <v>50.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="35">
@@ -887,7 +881,7 @@
         <v>50.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="36">
@@ -901,7 +895,7 @@
         <v>50.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>0.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="37">
@@ -929,7 +923,7 @@
         <v>50.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>72.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="39">
@@ -943,7 +937,7 @@
         <v>50.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>1.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="40">
@@ -951,13 +945,13 @@
         <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>85.0</v>
+        <v>90.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>50.0</v>
+        <v>45.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="41">
@@ -965,13 +959,13 @@
         <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>85.0</v>
+        <v>90.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>50.0</v>
+        <v>45.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>29.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="42">
@@ -985,7 +979,7 @@
         <v>45.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>10.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="43">
@@ -993,13 +987,13 @@
         <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>90.0</v>
+        <v>93.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>45.0</v>
+        <v>42.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>2.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="44">
@@ -1007,13 +1001,13 @@
         <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>90.0</v>
+        <v>93.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>45.0</v>
+        <v>42.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>29.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="45">
@@ -1027,7 +1021,7 @@
         <v>42.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>40.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="46">
@@ -1041,7 +1035,7 @@
         <v>42.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>14.0</v>
+        <v>121.0</v>
       </c>
     </row>
     <row r="47">
@@ -1049,13 +1043,13 @@
         <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>42.0</v>
+        <v>41.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>85.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="48">
@@ -1063,13 +1057,13 @@
         <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>42.0</v>
+        <v>41.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>121.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="49">
@@ -1083,7 +1077,7 @@
         <v>41.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>9.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="50">
@@ -1091,13 +1085,13 @@
         <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>94.0</v>
+        <v>95.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>41.0</v>
+        <v>40.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>26.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="51">
@@ -1105,13 +1099,13 @@
         <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>94.0</v>
+        <v>95.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>41.0</v>
+        <v>40.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>67.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="52">
@@ -1125,7 +1119,7 @@
         <v>40.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>54.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="53">
@@ -1139,7 +1133,7 @@
         <v>40.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>25.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="54">
@@ -1147,13 +1141,13 @@
         <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>95.0</v>
+        <v>101.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>40.0</v>
+        <v>34.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>23.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="55">
@@ -1161,13 +1155,13 @@
         <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>95.0</v>
+        <v>101.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>40.0</v>
+        <v>34.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>33.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="56">
@@ -1181,7 +1175,7 @@
         <v>34.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>3.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="57">
@@ -1195,7 +1189,7 @@
         <v>34.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="58">
@@ -1209,7 +1203,7 @@
         <v>34.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>44.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="59">
@@ -1223,7 +1217,7 @@
         <v>34.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="60">
@@ -1237,7 +1231,7 @@
         <v>34.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>0.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="61">
@@ -1245,13 +1239,13 @@
         <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>101.0</v>
+        <v>104.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>34.0</v>
+        <v>31.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="62">
@@ -1259,13 +1253,13 @@
         <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>101.0</v>
+        <v>104.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>34.0</v>
+        <v>31.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>58.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="63">
@@ -1279,7 +1273,7 @@
         <v>31.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="64">
@@ -1287,13 +1281,13 @@
         <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>104.0</v>
+        <v>106.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="65">
@@ -1301,13 +1295,13 @@
         <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>104.0</v>
+        <v>106.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="66">
@@ -1321,7 +1315,7 @@
         <v>29.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="67">
@@ -1335,7 +1329,7 @@
         <v>29.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="68">
@@ -1343,13 +1337,13 @@
         <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>106.0</v>
+        <v>110.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>29.0</v>
+        <v>25.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="69">
@@ -1357,10 +1351,10 @@
         <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>106.0</v>
+        <v>110.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>29.0</v>
+        <v>25.0</v>
       </c>
       <c r="D69" t="n" s="0">
         <v>0.0</v>
@@ -1385,13 +1379,13 @@
         <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>110.0</v>
+        <v>114.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>25.0</v>
+        <v>21.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="72">
@@ -1399,13 +1393,13 @@
         <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>110.0</v>
+        <v>114.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>25.0</v>
+        <v>21.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="73">
@@ -1419,7 +1413,7 @@
         <v>21.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="74">
@@ -1433,7 +1427,7 @@
         <v>21.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="75">
@@ -1441,13 +1435,13 @@
         <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>114.0</v>
+        <v>121.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>21.0</v>
+        <v>14.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="76">
@@ -1455,10 +1449,10 @@
         <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>114.0</v>
+        <v>121.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>21.0</v>
+        <v>14.0</v>
       </c>
       <c r="D76" t="n" s="0">
         <v>0.0</v>
@@ -1475,7 +1469,7 @@
         <v>14.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="78">
@@ -1483,13 +1477,13 @@
         <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>121.0</v>
+        <v>135.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="79">
@@ -1497,10 +1491,10 @@
         <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>121.0</v>
+        <v>135.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="D79" t="n" s="0">
         <v>0.0</v>
@@ -1517,7 +1511,7 @@
         <v>0.0</v>
       </c>
       <c r="D80" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="81">
@@ -1630,34 +1624,6 @@
       </c>
       <c r="D88" t="n" s="0">
         <v>0.0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="B89" t="n" s="0">
-        <v>135.0</v>
-      </c>
-      <c r="C89" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D89" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s" s="0">
-        <v>93</v>
-      </c>
-      <c r="B90" t="n" s="0">
-        <v>135.0</v>
-      </c>
-      <c r="C90" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D90" t="s" s="0">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1672,27 +1638,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="C1" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>95</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>96</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>97</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>98</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>99</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>100</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>104.0</v>
@@ -1700,13 +1666,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>4.0</v>
@@ -1714,13 +1680,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>3.0</v>
@@ -1728,13 +1694,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>15.0</v>
@@ -1742,13 +1708,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="C6" t="s" s="0">
         <v>104</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>106</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>9.0</v>
@@ -1766,16 +1732,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="C1" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>95</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>96</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1790,18 +1756,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export-old/Coverage.xlsx
+++ b/gsc-export-old/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="111">
   <si>
     <t>Date</t>
   </si>
@@ -29,15 +29,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-11-27</t>
+    <t>2025-11-28</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2025-11-28</t>
-  </si>
-  <si>
     <t>2025-11-29</t>
   </si>
   <si>
@@ -291,6 +288,15 @@
   </si>
   <si>
     <t>2026-02-21</t>
+  </si>
+  <si>
+    <t>2026-02-22</t>
+  </si>
+  <si>
+    <t>2026-02-23</t>
+  </si>
+  <si>
+    <t>2026-02-24</t>
   </si>
   <si>
     <t>Reason</t>
@@ -391,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -433,7 +439,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="4">
@@ -447,7 +453,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="5">
@@ -461,7 +467,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="6">
@@ -475,7 +481,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="7">
@@ -489,7 +495,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="8">
@@ -503,7 +509,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +523,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="10">
@@ -545,7 +551,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="12">
@@ -559,7 +565,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="13">
@@ -573,7 +579,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="14">
@@ -615,7 +621,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="17">
@@ -643,21 +649,21 @@
         <v>5</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>3.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="B19" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C19" t="s" s="0">
-        <v>5</v>
+      <c r="B19" t="n" s="0">
+        <v>73.0</v>
+      </c>
+      <c r="C19" t="n" s="0">
+        <v>62.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="20">
@@ -665,13 +671,13 @@
         <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>73.0</v>
+        <v>79.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>62.0</v>
+        <v>56.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="21">
@@ -699,7 +705,7 @@
         <v>56.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>9.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="23">
@@ -713,7 +719,7 @@
         <v>56.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>15.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="24">
@@ -741,7 +747,7 @@
         <v>56.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="26">
@@ -755,7 +761,7 @@
         <v>56.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="27">
@@ -769,7 +775,7 @@
         <v>56.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>12.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="28">
@@ -777,13 +783,13 @@
         <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>79.0</v>
+        <v>85.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>56.0</v>
+        <v>50.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="29">
@@ -797,7 +803,7 @@
         <v>50.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="30">
@@ -811,7 +817,7 @@
         <v>50.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="31">
@@ -853,7 +859,7 @@
         <v>50.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="34">
@@ -867,7 +873,7 @@
         <v>50.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="35">
@@ -881,7 +887,7 @@
         <v>50.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>1.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="36">
@@ -895,7 +901,7 @@
         <v>50.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>72.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="37">
@@ -909,7 +915,7 @@
         <v>50.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="38">
@@ -923,7 +929,7 @@
         <v>50.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>2.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="39">
@@ -931,13 +937,13 @@
         <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>85.0</v>
+        <v>90.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>50.0</v>
+        <v>45.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>29.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="40">
@@ -951,7 +957,7 @@
         <v>45.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="41">
@@ -965,7 +971,7 @@
         <v>45.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>2.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="42">
@@ -973,13 +979,13 @@
         <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>90.0</v>
+        <v>93.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>45.0</v>
+        <v>42.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>29.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="43">
@@ -993,7 +999,7 @@
         <v>42.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>40.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="44">
@@ -1007,7 +1013,7 @@
         <v>42.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>14.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="45">
@@ -1021,7 +1027,7 @@
         <v>42.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>85.0</v>
+        <v>121.0</v>
       </c>
     </row>
     <row r="46">
@@ -1029,13 +1035,13 @@
         <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>42.0</v>
+        <v>41.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>121.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="47">
@@ -1049,7 +1055,7 @@
         <v>41.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>9.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="48">
@@ -1063,7 +1069,7 @@
         <v>41.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>26.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="49">
@@ -1071,13 +1077,13 @@
         <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>94.0</v>
+        <v>95.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>41.0</v>
+        <v>40.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>67.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="50">
@@ -1091,7 +1097,7 @@
         <v>40.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>54.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="51">
@@ -1105,7 +1111,7 @@
         <v>40.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="52">
@@ -1119,7 +1125,7 @@
         <v>40.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>23.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="53">
@@ -1127,13 +1133,13 @@
         <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>95.0</v>
+        <v>101.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>40.0</v>
+        <v>34.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>33.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="54">
@@ -1147,7 +1153,7 @@
         <v>34.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>3.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="55">
@@ -1161,7 +1167,7 @@
         <v>34.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>13.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="56">
@@ -1175,7 +1181,7 @@
         <v>34.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>44.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="57">
@@ -1203,7 +1209,7 @@
         <v>34.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="59">
@@ -1217,7 +1223,7 @@
         <v>34.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>1.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="60">
@@ -1225,13 +1231,13 @@
         <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>101.0</v>
+        <v>104.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>34.0</v>
+        <v>31.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>58.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="61">
@@ -1245,7 +1251,7 @@
         <v>31.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="62">
@@ -1259,7 +1265,7 @@
         <v>31.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="63">
@@ -1267,13 +1273,13 @@
         <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>104.0</v>
+        <v>106.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="64">
@@ -1287,7 +1293,7 @@
         <v>29.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="65">
@@ -1301,7 +1307,7 @@
         <v>29.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="66">
@@ -1315,7 +1321,7 @@
         <v>29.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="67">
@@ -1323,10 +1329,10 @@
         <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>106.0</v>
+        <v>110.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>29.0</v>
+        <v>25.0</v>
       </c>
       <c r="D67" t="n" s="0">
         <v>0.0</v>
@@ -1365,13 +1371,13 @@
         <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>110.0</v>
+        <v>114.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>25.0</v>
+        <v>21.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="71">
@@ -1385,7 +1391,7 @@
         <v>21.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="72">
@@ -1399,7 +1405,7 @@
         <v>21.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="73">
@@ -1413,7 +1419,7 @@
         <v>21.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="74">
@@ -1421,13 +1427,13 @@
         <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>114.0</v>
+        <v>121.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>21.0</v>
+        <v>14.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="75">
@@ -1441,7 +1447,7 @@
         <v>14.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="76">
@@ -1463,13 +1469,13 @@
         <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>121.0</v>
+        <v>135.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="78">
@@ -1483,7 +1489,7 @@
         <v>0.0</v>
       </c>
       <c r="D78" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="79">
@@ -1624,6 +1630,34 @@
       </c>
       <c r="D88" t="n" s="0">
         <v>0.0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B89" t="n" s="0">
+        <v>135.0</v>
+      </c>
+      <c r="C89" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D89" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B90" t="n" s="0">
+        <v>135.0</v>
+      </c>
+      <c r="C90" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D90" t="s" s="0">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1638,27 +1672,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>104.0</v>
@@ -1666,13 +1700,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>99</v>
       </c>
-      <c r="B3" t="s" s="0">
-        <v>97</v>
-      </c>
       <c r="C3" t="s" s="0">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>4.0</v>
@@ -1680,13 +1714,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="C4" t="s" s="0">
         <v>100</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>97</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>98</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>3.0</v>
@@ -1694,13 +1728,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>15.0</v>
@@ -1708,13 +1742,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>9.0</v>
@@ -1732,16 +1766,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1756,18 +1790,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export-old/Coverage.xlsx
+++ b/gsc-export-old/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="110">
   <si>
     <t>Date</t>
   </si>
@@ -29,13 +29,10 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-11-28</t>
+    <t>2025-11-29</t>
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>2025-11-29</t>
   </si>
   <si>
     <t>2025-11-30</t>
@@ -397,7 +394,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -425,7 +422,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="3">
@@ -439,7 +436,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="4">
@@ -453,7 +450,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="5">
@@ -467,7 +464,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="6">
@@ -481,7 +478,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="7">
@@ -495,7 +492,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="8">
@@ -509,7 +506,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="9">
@@ -537,7 +534,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="11">
@@ -551,7 +548,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="12">
@@ -565,7 +562,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="13">
@@ -607,7 +604,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="16">
@@ -635,21 +632,21 @@
         <v>5</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>3.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B18" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C18" t="s" s="0">
-        <v>5</v>
+      <c r="B18" t="n" s="0">
+        <v>73.0</v>
+      </c>
+      <c r="C18" t="n" s="0">
+        <v>62.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="19">
@@ -657,13 +654,13 @@
         <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>73.0</v>
+        <v>79.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>62.0</v>
+        <v>56.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="20">
@@ -691,7 +688,7 @@
         <v>56.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>9.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="22">
@@ -705,7 +702,7 @@
         <v>56.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>15.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="23">
@@ -733,7 +730,7 @@
         <v>56.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="25">
@@ -747,7 +744,7 @@
         <v>56.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="26">
@@ -761,7 +758,7 @@
         <v>56.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>12.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="27">
@@ -769,13 +766,13 @@
         <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>79.0</v>
+        <v>85.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>56.0</v>
+        <v>50.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="28">
@@ -789,7 +786,7 @@
         <v>50.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="29">
@@ -803,7 +800,7 @@
         <v>50.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="30">
@@ -845,7 +842,7 @@
         <v>50.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="33">
@@ -859,7 +856,7 @@
         <v>50.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="34">
@@ -873,7 +870,7 @@
         <v>50.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>1.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="35">
@@ -887,7 +884,7 @@
         <v>50.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>72.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="36">
@@ -901,7 +898,7 @@
         <v>50.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="37">
@@ -915,7 +912,7 @@
         <v>50.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>2.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="38">
@@ -923,13 +920,13 @@
         <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>85.0</v>
+        <v>90.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>50.0</v>
+        <v>45.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>29.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="39">
@@ -943,7 +940,7 @@
         <v>45.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="40">
@@ -957,7 +954,7 @@
         <v>45.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>2.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="41">
@@ -965,13 +962,13 @@
         <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>90.0</v>
+        <v>93.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>45.0</v>
+        <v>42.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>29.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="42">
@@ -985,7 +982,7 @@
         <v>42.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>40.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="43">
@@ -999,7 +996,7 @@
         <v>42.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>14.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="44">
@@ -1013,7 +1010,7 @@
         <v>42.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>85.0</v>
+        <v>121.0</v>
       </c>
     </row>
     <row r="45">
@@ -1021,13 +1018,13 @@
         <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>42.0</v>
+        <v>41.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>121.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="46">
@@ -1041,7 +1038,7 @@
         <v>41.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>9.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="47">
@@ -1055,7 +1052,7 @@
         <v>41.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>26.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="48">
@@ -1063,13 +1060,13 @@
         <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>94.0</v>
+        <v>95.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>41.0</v>
+        <v>40.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>67.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="49">
@@ -1083,7 +1080,7 @@
         <v>40.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>54.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="50">
@@ -1097,7 +1094,7 @@
         <v>40.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="51">
@@ -1111,7 +1108,7 @@
         <v>40.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>23.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="52">
@@ -1119,13 +1116,13 @@
         <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>95.0</v>
+        <v>101.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>40.0</v>
+        <v>34.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>33.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="53">
@@ -1139,7 +1136,7 @@
         <v>34.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>3.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="54">
@@ -1153,7 +1150,7 @@
         <v>34.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>13.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="55">
@@ -1167,7 +1164,7 @@
         <v>34.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>44.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="56">
@@ -1195,7 +1192,7 @@
         <v>34.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="58">
@@ -1209,7 +1206,7 @@
         <v>34.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>1.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="59">
@@ -1217,13 +1214,13 @@
         <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>101.0</v>
+        <v>104.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>34.0</v>
+        <v>31.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>58.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="60">
@@ -1237,7 +1234,7 @@
         <v>31.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="61">
@@ -1251,7 +1248,7 @@
         <v>31.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="62">
@@ -1259,13 +1256,13 @@
         <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>104.0</v>
+        <v>106.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="63">
@@ -1279,7 +1276,7 @@
         <v>29.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="64">
@@ -1293,7 +1290,7 @@
         <v>29.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="65">
@@ -1307,7 +1304,7 @@
         <v>29.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="66">
@@ -1315,10 +1312,10 @@
         <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>106.0</v>
+        <v>110.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>29.0</v>
+        <v>25.0</v>
       </c>
       <c r="D66" t="n" s="0">
         <v>0.0</v>
@@ -1357,13 +1354,13 @@
         <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>110.0</v>
+        <v>114.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>25.0</v>
+        <v>21.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="70">
@@ -1377,7 +1374,7 @@
         <v>21.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="71">
@@ -1391,7 +1388,7 @@
         <v>21.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="72">
@@ -1405,7 +1402,7 @@
         <v>21.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="73">
@@ -1413,13 +1410,13 @@
         <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>114.0</v>
+        <v>121.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>21.0</v>
+        <v>14.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="74">
@@ -1433,7 +1430,7 @@
         <v>14.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="75">
@@ -1455,13 +1452,13 @@
         <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>121.0</v>
+        <v>135.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="77">
@@ -1475,7 +1472,7 @@
         <v>0.0</v>
       </c>
       <c r="D77" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="78">
@@ -1644,20 +1641,6 @@
       </c>
       <c r="D89" t="n" s="0">
         <v>0.0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s" s="0">
-        <v>93</v>
-      </c>
-      <c r="B90" t="n" s="0">
-        <v>135.0</v>
-      </c>
-      <c r="C90" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D90" t="s" s="0">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1672,27 +1655,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>95</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>96</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>97</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>98</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="C2" t="s" s="0">
         <v>99</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>100</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>104.0</v>
@@ -1700,13 +1683,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B3" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="C3" t="s" s="0">
         <v>99</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>100</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>4.0</v>
@@ -1714,13 +1697,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B4" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="C4" t="s" s="0">
         <v>99</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>100</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>3.0</v>
@@ -1728,13 +1711,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="B5" t="s" s="0">
         <v>103</v>
       </c>
-      <c r="B5" t="s" s="0">
-        <v>104</v>
-      </c>
       <c r="C5" t="s" s="0">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>15.0</v>
@@ -1742,13 +1725,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="C6" t="s" s="0">
         <v>105</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>104</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>106</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>9.0</v>
@@ -1766,16 +1749,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>95</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>96</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -1790,18 +1773,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>107</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>108</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>109</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export-old/Coverage.xlsx
+++ b/gsc-export-old/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="109">
   <si>
     <t>Date</t>
   </si>
@@ -29,13 +29,10 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-11-29</t>
+    <t>2025-11-30</t>
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>2025-11-30</t>
   </si>
   <si>
     <t>2025-12-01</t>
@@ -394,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -422,7 +419,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="3">
@@ -436,7 +433,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="4">
@@ -450,7 +447,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="5">
@@ -464,7 +461,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="6">
@@ -478,7 +475,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="7">
@@ -492,7 +489,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="8">
@@ -520,7 +517,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="10">
@@ -534,7 +531,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="11">
@@ -548,7 +545,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="12">
@@ -590,7 +587,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="15">
@@ -618,21 +615,21 @@
         <v>5</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>3.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
         <v>20</v>
       </c>
-      <c r="B17" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C17" t="s" s="0">
-        <v>5</v>
+      <c r="B17" t="n" s="0">
+        <v>73.0</v>
+      </c>
+      <c r="C17" t="n" s="0">
+        <v>62.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="18">
@@ -640,13 +637,13 @@
         <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>73.0</v>
+        <v>79.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>62.0</v>
+        <v>56.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="19">
@@ -674,7 +671,7 @@
         <v>56.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>9.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="21">
@@ -688,7 +685,7 @@
         <v>56.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>15.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="22">
@@ -716,7 +713,7 @@
         <v>56.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="24">
@@ -730,7 +727,7 @@
         <v>56.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="25">
@@ -744,7 +741,7 @@
         <v>56.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>12.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="26">
@@ -752,13 +749,13 @@
         <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>79.0</v>
+        <v>85.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>56.0</v>
+        <v>50.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="27">
@@ -772,7 +769,7 @@
         <v>50.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="28">
@@ -786,7 +783,7 @@
         <v>50.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="29">
@@ -828,7 +825,7 @@
         <v>50.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="32">
@@ -842,7 +839,7 @@
         <v>50.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="33">
@@ -856,7 +853,7 @@
         <v>50.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>1.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="34">
@@ -870,7 +867,7 @@
         <v>50.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>72.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="35">
@@ -884,7 +881,7 @@
         <v>50.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="36">
@@ -898,7 +895,7 @@
         <v>50.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>2.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="37">
@@ -906,13 +903,13 @@
         <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>85.0</v>
+        <v>90.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>50.0</v>
+        <v>45.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>29.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="38">
@@ -926,7 +923,7 @@
         <v>45.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="39">
@@ -940,7 +937,7 @@
         <v>45.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>2.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="40">
@@ -948,13 +945,13 @@
         <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>90.0</v>
+        <v>93.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>45.0</v>
+        <v>42.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>29.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="41">
@@ -968,7 +965,7 @@
         <v>42.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>40.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="42">
@@ -982,7 +979,7 @@
         <v>42.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>14.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="43">
@@ -996,7 +993,7 @@
         <v>42.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>85.0</v>
+        <v>121.0</v>
       </c>
     </row>
     <row r="44">
@@ -1004,13 +1001,13 @@
         <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>42.0</v>
+        <v>41.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>121.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="45">
@@ -1024,7 +1021,7 @@
         <v>41.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>9.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="46">
@@ -1038,7 +1035,7 @@
         <v>41.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>26.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="47">
@@ -1046,13 +1043,13 @@
         <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>94.0</v>
+        <v>95.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>41.0</v>
+        <v>40.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>67.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="48">
@@ -1066,7 +1063,7 @@
         <v>40.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>54.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="49">
@@ -1080,7 +1077,7 @@
         <v>40.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="50">
@@ -1094,7 +1091,7 @@
         <v>40.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>23.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="51">
@@ -1102,13 +1099,13 @@
         <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>95.0</v>
+        <v>101.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>40.0</v>
+        <v>34.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>33.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="52">
@@ -1122,7 +1119,7 @@
         <v>34.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>3.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="53">
@@ -1136,7 +1133,7 @@
         <v>34.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>13.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="54">
@@ -1150,7 +1147,7 @@
         <v>34.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>44.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="55">
@@ -1178,7 +1175,7 @@
         <v>34.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="57">
@@ -1192,7 +1189,7 @@
         <v>34.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>1.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="58">
@@ -1200,13 +1197,13 @@
         <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>101.0</v>
+        <v>104.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>34.0</v>
+        <v>31.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>58.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="59">
@@ -1220,7 +1217,7 @@
         <v>31.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="60">
@@ -1234,7 +1231,7 @@
         <v>31.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="61">
@@ -1242,13 +1239,13 @@
         <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>104.0</v>
+        <v>106.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="62">
@@ -1262,7 +1259,7 @@
         <v>29.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="63">
@@ -1276,7 +1273,7 @@
         <v>29.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="64">
@@ -1290,7 +1287,7 @@
         <v>29.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="65">
@@ -1298,10 +1295,10 @@
         <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>106.0</v>
+        <v>110.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>29.0</v>
+        <v>25.0</v>
       </c>
       <c r="D65" t="n" s="0">
         <v>0.0</v>
@@ -1340,13 +1337,13 @@
         <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>110.0</v>
+        <v>114.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>25.0</v>
+        <v>21.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="69">
@@ -1360,7 +1357,7 @@
         <v>21.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="70">
@@ -1374,7 +1371,7 @@
         <v>21.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="71">
@@ -1388,7 +1385,7 @@
         <v>21.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="72">
@@ -1396,13 +1393,13 @@
         <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>114.0</v>
+        <v>121.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>21.0</v>
+        <v>14.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="73">
@@ -1416,7 +1413,7 @@
         <v>14.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="74">
@@ -1438,13 +1435,13 @@
         <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>121.0</v>
+        <v>135.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="76">
@@ -1458,7 +1455,7 @@
         <v>0.0</v>
       </c>
       <c r="D76" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="77">
@@ -1626,20 +1623,6 @@
         <v>0.0</v>
       </c>
       <c r="D88" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="B89" t="n" s="0">
-        <v>135.0</v>
-      </c>
-      <c r="C89" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D89" t="n" s="0">
         <v>0.0</v>
       </c>
     </row>
@@ -1655,27 +1638,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>95</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>96</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>97</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="C2" t="s" s="0">
         <v>98</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>99</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>104.0</v>
@@ -1683,13 +1666,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B3" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="C3" t="s" s="0">
         <v>98</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>99</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>4.0</v>
@@ -1697,13 +1680,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="C4" t="s" s="0">
         <v>98</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>99</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>3.0</v>
@@ -1711,13 +1694,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="B5" t="s" s="0">
         <v>102</v>
       </c>
-      <c r="B5" t="s" s="0">
-        <v>103</v>
-      </c>
       <c r="C5" t="s" s="0">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>15.0</v>
@@ -1725,13 +1708,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="C6" t="s" s="0">
         <v>104</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>103</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>105</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>9.0</v>
@@ -1749,16 +1732,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>95</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1773,18 +1756,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>106</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>107</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>108</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export-old/Coverage.xlsx
+++ b/gsc-export-old/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="107">
   <si>
     <t>Date</t>
   </si>
@@ -29,16 +29,10 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-11-30</t>
+    <t>2025-12-02</t>
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>2025-12-01</t>
-  </si>
-  <si>
-    <t>2025-12-02</t>
   </si>
   <si>
     <t>2025-12-03</t>
@@ -391,7 +385,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -419,7 +413,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="3">
@@ -433,7 +427,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="4">
@@ -447,7 +441,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="5">
@@ -461,7 +455,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="6">
@@ -475,7 +469,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="7">
@@ -489,7 +483,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="8">
@@ -503,7 +497,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +511,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="10">
@@ -531,7 +525,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="11">
@@ -559,7 +553,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="13">
@@ -573,7 +567,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="14">
@@ -587,35 +581,35 @@
         <v>5</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>3.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="B15" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C15" t="s" s="0">
-        <v>5</v>
+      <c r="B15" t="n" s="0">
+        <v>73.0</v>
+      </c>
+      <c r="C15" t="n" s="0">
+        <v>62.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="B16" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C16" t="s" s="0">
-        <v>5</v>
+      <c r="B16" t="n" s="0">
+        <v>79.0</v>
+      </c>
+      <c r="C16" t="n" s="0">
+        <v>56.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>16.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="17">
@@ -623,13 +617,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>73.0</v>
+        <v>79.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>62.0</v>
+        <v>56.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="18">
@@ -643,7 +637,7 @@
         <v>56.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>9.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="19">
@@ -657,7 +651,7 @@
         <v>56.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="20">
@@ -671,7 +665,7 @@
         <v>56.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>15.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="21">
@@ -685,7 +679,7 @@
         <v>56.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="22">
@@ -699,7 +693,7 @@
         <v>56.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>7.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="23">
@@ -713,7 +707,7 @@
         <v>56.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="24">
@@ -721,13 +715,13 @@
         <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>79.0</v>
+        <v>85.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>56.0</v>
+        <v>50.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="25">
@@ -735,13 +729,13 @@
         <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>79.0</v>
+        <v>85.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>56.0</v>
+        <v>50.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="26">
@@ -755,7 +749,7 @@
         <v>50.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="27">
@@ -769,7 +763,7 @@
         <v>50.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="28">
@@ -797,7 +791,7 @@
         <v>50.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="30">
@@ -811,7 +805,7 @@
         <v>50.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="31">
@@ -825,7 +819,7 @@
         <v>50.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>0.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="32">
@@ -853,7 +847,7 @@
         <v>50.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>72.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="34">
@@ -867,7 +861,7 @@
         <v>50.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>1.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="35">
@@ -875,13 +869,13 @@
         <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>85.0</v>
+        <v>90.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>50.0</v>
+        <v>45.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="36">
@@ -889,13 +883,13 @@
         <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>85.0</v>
+        <v>90.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>50.0</v>
+        <v>45.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>29.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="37">
@@ -909,7 +903,7 @@
         <v>45.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>10.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="38">
@@ -917,13 +911,13 @@
         <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>90.0</v>
+        <v>93.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>45.0</v>
+        <v>42.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>2.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="39">
@@ -931,13 +925,13 @@
         <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>90.0</v>
+        <v>93.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>45.0</v>
+        <v>42.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>29.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="40">
@@ -951,7 +945,7 @@
         <v>42.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>40.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="41">
@@ -965,7 +959,7 @@
         <v>42.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>14.0</v>
+        <v>121.0</v>
       </c>
     </row>
     <row r="42">
@@ -973,13 +967,13 @@
         <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>42.0</v>
+        <v>41.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>85.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="43">
@@ -987,13 +981,13 @@
         <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>42.0</v>
+        <v>41.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>121.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="44">
@@ -1007,7 +1001,7 @@
         <v>41.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>9.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="45">
@@ -1015,13 +1009,13 @@
         <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>94.0</v>
+        <v>95.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>41.0</v>
+        <v>40.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>26.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="46">
@@ -1029,13 +1023,13 @@
         <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>94.0</v>
+        <v>95.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>41.0</v>
+        <v>40.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>67.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="47">
@@ -1049,7 +1043,7 @@
         <v>40.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>54.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="48">
@@ -1063,7 +1057,7 @@
         <v>40.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>25.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="49">
@@ -1071,13 +1065,13 @@
         <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>95.0</v>
+        <v>101.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>40.0</v>
+        <v>34.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>23.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="50">
@@ -1085,13 +1079,13 @@
         <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>95.0</v>
+        <v>101.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>40.0</v>
+        <v>34.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>33.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="51">
@@ -1105,7 +1099,7 @@
         <v>34.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>3.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="52">
@@ -1119,7 +1113,7 @@
         <v>34.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="53">
@@ -1133,7 +1127,7 @@
         <v>34.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>44.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="54">
@@ -1147,7 +1141,7 @@
         <v>34.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="55">
@@ -1161,7 +1155,7 @@
         <v>34.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>0.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="56">
@@ -1169,13 +1163,13 @@
         <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>101.0</v>
+        <v>104.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>34.0</v>
+        <v>31.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="57">
@@ -1183,13 +1177,13 @@
         <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>101.0</v>
+        <v>104.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>34.0</v>
+        <v>31.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>58.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="58">
@@ -1203,7 +1197,7 @@
         <v>31.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="59">
@@ -1211,13 +1205,13 @@
         <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>104.0</v>
+        <v>106.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="60">
@@ -1225,13 +1219,13 @@
         <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>104.0</v>
+        <v>106.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="61">
@@ -1245,7 +1239,7 @@
         <v>29.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="62">
@@ -1259,7 +1253,7 @@
         <v>29.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="63">
@@ -1267,13 +1261,13 @@
         <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>106.0</v>
+        <v>110.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>29.0</v>
+        <v>25.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="64">
@@ -1281,10 +1275,10 @@
         <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>106.0</v>
+        <v>110.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>29.0</v>
+        <v>25.0</v>
       </c>
       <c r="D64" t="n" s="0">
         <v>0.0</v>
@@ -1309,13 +1303,13 @@
         <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>110.0</v>
+        <v>114.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>25.0</v>
+        <v>21.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="67">
@@ -1323,13 +1317,13 @@
         <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>110.0</v>
+        <v>114.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>25.0</v>
+        <v>21.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="68">
@@ -1343,7 +1337,7 @@
         <v>21.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="69">
@@ -1357,7 +1351,7 @@
         <v>21.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="70">
@@ -1365,13 +1359,13 @@
         <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>114.0</v>
+        <v>121.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>21.0</v>
+        <v>14.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="71">
@@ -1379,10 +1373,10 @@
         <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>114.0</v>
+        <v>121.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>21.0</v>
+        <v>14.0</v>
       </c>
       <c r="D71" t="n" s="0">
         <v>0.0</v>
@@ -1399,7 +1393,7 @@
         <v>14.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="73">
@@ -1407,13 +1401,13 @@
         <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>121.0</v>
+        <v>135.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="74">
@@ -1421,10 +1415,10 @@
         <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>121.0</v>
+        <v>135.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="D74" t="n" s="0">
         <v>0.0</v>
@@ -1441,7 +1435,7 @@
         <v>0.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="76">
@@ -1595,34 +1589,6 @@
         <v>0.0</v>
       </c>
       <c r="D86" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s" s="0">
-        <v>90</v>
-      </c>
-      <c r="B87" t="n" s="0">
-        <v>135.0</v>
-      </c>
-      <c r="C87" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D87" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s" s="0">
-        <v>91</v>
-      </c>
-      <c r="B88" t="n" s="0">
-        <v>135.0</v>
-      </c>
-      <c r="C88" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D88" t="n" s="0">
         <v>0.0</v>
       </c>
     </row>
@@ -1638,27 +1604,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="C1" t="s" s="0">
         <v>92</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>93</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>94</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>95</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>96</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>97</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>98</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>104.0</v>
@@ -1666,13 +1632,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>4.0</v>
@@ -1680,13 +1646,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>3.0</v>
@@ -1694,13 +1660,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>15.0</v>
@@ -1708,13 +1674,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B6" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="C6" t="s" s="0">
         <v>102</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>104</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>9.0</v>
@@ -1732,16 +1698,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="C1" t="s" s="0">
         <v>92</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>93</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>94</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -1756,18 +1722,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export-old/Coverage.xlsx
+++ b/gsc-export-old/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="106">
   <si>
     <t>Date</t>
   </si>
@@ -29,13 +29,10 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-12-02</t>
+    <t>2025-12-03</t>
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>2025-12-03</t>
   </si>
   <si>
     <t>2025-12-04</t>
@@ -385,7 +382,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -413,7 +410,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="3">
@@ -427,7 +424,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="4">
@@ -441,7 +438,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +466,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="7">
@@ -483,7 +480,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="8">
@@ -497,7 +494,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="9">
@@ -539,7 +536,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="12">
@@ -567,21 +564,21 @@
         <v>5</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>3.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
         <v>17</v>
       </c>
-      <c r="B14" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C14" t="s" s="0">
-        <v>5</v>
+      <c r="B14" t="n" s="0">
+        <v>73.0</v>
+      </c>
+      <c r="C14" t="n" s="0">
+        <v>62.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="15">
@@ -589,13 +586,13 @@
         <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>73.0</v>
+        <v>79.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>62.0</v>
+        <v>56.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="16">
@@ -623,7 +620,7 @@
         <v>56.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>9.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="18">
@@ -637,7 +634,7 @@
         <v>56.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>15.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="19">
@@ -665,7 +662,7 @@
         <v>56.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="21">
@@ -679,7 +676,7 @@
         <v>56.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="22">
@@ -693,7 +690,7 @@
         <v>56.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>12.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="23">
@@ -701,13 +698,13 @@
         <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>79.0</v>
+        <v>85.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>56.0</v>
+        <v>50.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="24">
@@ -721,7 +718,7 @@
         <v>50.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="25">
@@ -735,7 +732,7 @@
         <v>50.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="26">
@@ -777,7 +774,7 @@
         <v>50.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="29">
@@ -791,7 +788,7 @@
         <v>50.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="30">
@@ -805,7 +802,7 @@
         <v>50.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>1.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="31">
@@ -819,7 +816,7 @@
         <v>50.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>72.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="32">
@@ -833,7 +830,7 @@
         <v>50.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="33">
@@ -847,7 +844,7 @@
         <v>50.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>2.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="34">
@@ -855,13 +852,13 @@
         <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>85.0</v>
+        <v>90.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>50.0</v>
+        <v>45.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>29.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="35">
@@ -875,7 +872,7 @@
         <v>45.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="36">
@@ -889,7 +886,7 @@
         <v>45.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>2.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="37">
@@ -897,13 +894,13 @@
         <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>90.0</v>
+        <v>93.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>45.0</v>
+        <v>42.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>29.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="38">
@@ -917,7 +914,7 @@
         <v>42.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>40.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="39">
@@ -931,7 +928,7 @@
         <v>42.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>14.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="40">
@@ -945,7 +942,7 @@
         <v>42.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>85.0</v>
+        <v>121.0</v>
       </c>
     </row>
     <row r="41">
@@ -953,13 +950,13 @@
         <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>42.0</v>
+        <v>41.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>121.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="42">
@@ -973,7 +970,7 @@
         <v>41.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>9.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="43">
@@ -987,7 +984,7 @@
         <v>41.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>26.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="44">
@@ -995,13 +992,13 @@
         <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>94.0</v>
+        <v>95.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>41.0</v>
+        <v>40.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>67.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="45">
@@ -1015,7 +1012,7 @@
         <v>40.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>54.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="46">
@@ -1029,7 +1026,7 @@
         <v>40.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="47">
@@ -1043,7 +1040,7 @@
         <v>40.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>23.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="48">
@@ -1051,13 +1048,13 @@
         <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>95.0</v>
+        <v>101.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>40.0</v>
+        <v>34.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>33.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="49">
@@ -1071,7 +1068,7 @@
         <v>34.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>3.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="50">
@@ -1085,7 +1082,7 @@
         <v>34.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>13.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="51">
@@ -1099,7 +1096,7 @@
         <v>34.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>44.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="52">
@@ -1127,7 +1124,7 @@
         <v>34.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="54">
@@ -1141,7 +1138,7 @@
         <v>34.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>1.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="55">
@@ -1149,13 +1146,13 @@
         <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>101.0</v>
+        <v>104.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>34.0</v>
+        <v>31.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>58.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="56">
@@ -1169,7 +1166,7 @@
         <v>31.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="57">
@@ -1183,7 +1180,7 @@
         <v>31.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="58">
@@ -1191,13 +1188,13 @@
         <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>104.0</v>
+        <v>106.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="59">
@@ -1211,7 +1208,7 @@
         <v>29.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="60">
@@ -1225,7 +1222,7 @@
         <v>29.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="61">
@@ -1239,7 +1236,7 @@
         <v>29.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="62">
@@ -1247,10 +1244,10 @@
         <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>106.0</v>
+        <v>110.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>29.0</v>
+        <v>25.0</v>
       </c>
       <c r="D62" t="n" s="0">
         <v>0.0</v>
@@ -1289,13 +1286,13 @@
         <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>110.0</v>
+        <v>114.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>25.0</v>
+        <v>21.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="66">
@@ -1309,7 +1306,7 @@
         <v>21.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="67">
@@ -1323,7 +1320,7 @@
         <v>21.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="68">
@@ -1337,7 +1334,7 @@
         <v>21.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="69">
@@ -1345,13 +1342,13 @@
         <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>114.0</v>
+        <v>121.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>21.0</v>
+        <v>14.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="70">
@@ -1365,7 +1362,7 @@
         <v>14.0</v>
       </c>
       <c r="D70" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="71">
@@ -1387,13 +1384,13 @@
         <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>121.0</v>
+        <v>135.0</v>
       </c>
       <c r="C72" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="73">
@@ -1407,7 +1404,7 @@
         <v>0.0</v>
       </c>
       <c r="D73" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="74">
@@ -1575,20 +1572,6 @@
         <v>0.0</v>
       </c>
       <c r="D85" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s" s="0">
-        <v>89</v>
-      </c>
-      <c r="B86" t="n" s="0">
-        <v>135.0</v>
-      </c>
-      <c r="C86" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D86" t="n" s="0">
         <v>0.0</v>
       </c>
     </row>
@@ -1604,27 +1587,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>90</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>91</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>92</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>93</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>94</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="C2" t="s" s="0">
         <v>95</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>96</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>104.0</v>
@@ -1632,13 +1615,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B3" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="C3" t="s" s="0">
         <v>95</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>96</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>4.0</v>
@@ -1646,13 +1629,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B4" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="C4" t="s" s="0">
         <v>95</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>96</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>3.0</v>
@@ -1660,13 +1643,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="B5" t="s" s="0">
         <v>99</v>
       </c>
-      <c r="B5" t="s" s="0">
-        <v>100</v>
-      </c>
       <c r="C5" t="s" s="0">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>15.0</v>
@@ -1674,13 +1657,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="C6" t="s" s="0">
         <v>101</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>100</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>102</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>9.0</v>
@@ -1698,16 +1681,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>90</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>91</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>92</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1722,18 +1705,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>103</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>104</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>105</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export-old/Coverage.xlsx
+++ b/gsc-export-old/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="105">
   <si>
     <t>Date</t>
   </si>
@@ -29,13 +29,10 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-12-03</t>
+    <t>2025-12-04</t>
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>2025-12-04</t>
   </si>
   <si>
     <t>2025-12-05</t>
@@ -382,7 +379,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -410,7 +407,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="3">
@@ -424,7 +421,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="4">
@@ -452,7 +449,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="6">
@@ -466,7 +463,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="7">
@@ -480,7 +477,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="8">
@@ -522,7 +519,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="11">
@@ -550,21 +547,21 @@
         <v>5</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>3.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="B13" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C13" t="s" s="0">
-        <v>5</v>
+      <c r="B13" t="n" s="0">
+        <v>73.0</v>
+      </c>
+      <c r="C13" t="n" s="0">
+        <v>62.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>16.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="14">
@@ -572,13 +569,13 @@
         <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>73.0</v>
+        <v>79.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>62.0</v>
+        <v>56.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="15">
@@ -606,7 +603,7 @@
         <v>56.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>9.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="17">
@@ -620,7 +617,7 @@
         <v>56.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>15.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="18">
@@ -648,7 +645,7 @@
         <v>56.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="20">
@@ -662,7 +659,7 @@
         <v>56.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="21">
@@ -676,7 +673,7 @@
         <v>56.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>12.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="22">
@@ -684,13 +681,13 @@
         <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>79.0</v>
+        <v>85.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>56.0</v>
+        <v>50.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="23">
@@ -704,7 +701,7 @@
         <v>50.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="24">
@@ -718,7 +715,7 @@
         <v>50.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="25">
@@ -760,7 +757,7 @@
         <v>50.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="28">
@@ -774,7 +771,7 @@
         <v>50.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="29">
@@ -788,7 +785,7 @@
         <v>50.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>1.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="30">
@@ -802,7 +799,7 @@
         <v>50.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>72.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="31">
@@ -816,7 +813,7 @@
         <v>50.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="32">
@@ -830,7 +827,7 @@
         <v>50.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>2.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="33">
@@ -838,13 +835,13 @@
         <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>85.0</v>
+        <v>90.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>50.0</v>
+        <v>45.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>29.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="34">
@@ -858,7 +855,7 @@
         <v>45.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="35">
@@ -872,7 +869,7 @@
         <v>45.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>2.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="36">
@@ -880,13 +877,13 @@
         <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>90.0</v>
+        <v>93.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>45.0</v>
+        <v>42.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>29.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="37">
@@ -900,7 +897,7 @@
         <v>42.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>40.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="38">
@@ -914,7 +911,7 @@
         <v>42.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>14.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="39">
@@ -928,7 +925,7 @@
         <v>42.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>85.0</v>
+        <v>121.0</v>
       </c>
     </row>
     <row r="40">
@@ -936,13 +933,13 @@
         <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>42.0</v>
+        <v>41.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>121.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="41">
@@ -956,7 +953,7 @@
         <v>41.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>9.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="42">
@@ -970,7 +967,7 @@
         <v>41.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>26.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="43">
@@ -978,13 +975,13 @@
         <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>94.0</v>
+        <v>95.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>41.0</v>
+        <v>40.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>67.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="44">
@@ -998,7 +995,7 @@
         <v>40.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>54.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="45">
@@ -1012,7 +1009,7 @@
         <v>40.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="46">
@@ -1026,7 +1023,7 @@
         <v>40.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>23.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="47">
@@ -1034,13 +1031,13 @@
         <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>95.0</v>
+        <v>101.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>40.0</v>
+        <v>34.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>33.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="48">
@@ -1054,7 +1051,7 @@
         <v>34.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>3.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="49">
@@ -1068,7 +1065,7 @@
         <v>34.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>13.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="50">
@@ -1082,7 +1079,7 @@
         <v>34.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>44.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="51">
@@ -1110,7 +1107,7 @@
         <v>34.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="53">
@@ -1124,7 +1121,7 @@
         <v>34.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>1.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="54">
@@ -1132,13 +1129,13 @@
         <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>101.0</v>
+        <v>104.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>34.0</v>
+        <v>31.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>58.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="55">
@@ -1152,7 +1149,7 @@
         <v>31.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="56">
@@ -1166,7 +1163,7 @@
         <v>31.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="57">
@@ -1174,13 +1171,13 @@
         <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>104.0</v>
+        <v>106.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="58">
@@ -1194,7 +1191,7 @@
         <v>29.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="59">
@@ -1208,7 +1205,7 @@
         <v>29.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="60">
@@ -1222,7 +1219,7 @@
         <v>29.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="61">
@@ -1230,10 +1227,10 @@
         <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>106.0</v>
+        <v>110.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>29.0</v>
+        <v>25.0</v>
       </c>
       <c r="D61" t="n" s="0">
         <v>0.0</v>
@@ -1272,13 +1269,13 @@
         <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>110.0</v>
+        <v>114.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>25.0</v>
+        <v>21.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="65">
@@ -1292,7 +1289,7 @@
         <v>21.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="66">
@@ -1306,7 +1303,7 @@
         <v>21.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="67">
@@ -1320,7 +1317,7 @@
         <v>21.0</v>
       </c>
       <c r="D67" t="n" s="0">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="68">
@@ -1328,13 +1325,13 @@
         <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>114.0</v>
+        <v>121.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>21.0</v>
+        <v>14.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="69">
@@ -1348,7 +1345,7 @@
         <v>14.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="70">
@@ -1370,13 +1367,13 @@
         <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>121.0</v>
+        <v>135.0</v>
       </c>
       <c r="C71" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="72">
@@ -1390,7 +1387,7 @@
         <v>0.0</v>
       </c>
       <c r="D72" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="73">
@@ -1558,20 +1555,6 @@
         <v>0.0</v>
       </c>
       <c r="D84" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s" s="0">
-        <v>88</v>
-      </c>
-      <c r="B85" t="n" s="0">
-        <v>135.0</v>
-      </c>
-      <c r="C85" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D85" t="n" s="0">
         <v>0.0</v>
       </c>
     </row>
@@ -1587,27 +1570,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>89</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>90</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>91</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>92</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="C2" t="s" s="0">
         <v>94</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>95</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>104.0</v>
@@ -1615,13 +1598,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B3" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="C3" t="s" s="0">
         <v>94</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>95</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>4.0</v>
@@ -1629,13 +1612,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B4" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="C4" t="s" s="0">
         <v>94</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>95</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>3.0</v>
@@ -1643,13 +1626,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B5" t="s" s="0">
         <v>98</v>
       </c>
-      <c r="B5" t="s" s="0">
-        <v>99</v>
-      </c>
       <c r="C5" t="s" s="0">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>15.0</v>
@@ -1657,13 +1640,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="C6" t="s" s="0">
         <v>100</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>99</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>101</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>9.0</v>
@@ -1681,16 +1664,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>89</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>90</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>91</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -1705,18 +1688,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>102</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>103</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>104</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export-old/Coverage.xlsx
+++ b/gsc-export-old/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="103">
   <si>
     <t>Date</t>
   </si>
@@ -29,16 +29,10 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-12-04</t>
+    <t>2025-12-06</t>
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>2025-12-05</t>
-  </si>
-  <si>
-    <t>2025-12-06</t>
   </si>
   <si>
     <t>2025-12-07</t>
@@ -379,7 +373,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -407,7 +401,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="3">
@@ -421,7 +415,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="4">
@@ -435,7 +429,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="5">
@@ -449,7 +443,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="6">
@@ -463,7 +457,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="7">
@@ -491,7 +485,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="9">
@@ -505,7 +499,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="10">
@@ -519,35 +513,35 @@
         <v>5</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>3.0</v>
+        <v>16.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B11" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C11" t="s" s="0">
-        <v>5</v>
+      <c r="B11" t="n" s="0">
+        <v>73.0</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>62.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
         <v>15</v>
       </c>
-      <c r="B12" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C12" t="s" s="0">
-        <v>5</v>
+      <c r="B12" t="n" s="0">
+        <v>79.0</v>
+      </c>
+      <c r="C12" t="n" s="0">
+        <v>56.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>16.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="13">
@@ -555,13 +549,13 @@
         <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>73.0</v>
+        <v>79.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>62.0</v>
+        <v>56.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="14">
@@ -575,7 +569,7 @@
         <v>56.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>9.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="15">
@@ -589,7 +583,7 @@
         <v>56.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="16">
@@ -603,7 +597,7 @@
         <v>56.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>15.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="17">
@@ -617,7 +611,7 @@
         <v>56.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="18">
@@ -631,7 +625,7 @@
         <v>56.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>7.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="19">
@@ -645,7 +639,7 @@
         <v>56.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="20">
@@ -653,13 +647,13 @@
         <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>79.0</v>
+        <v>85.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>56.0</v>
+        <v>50.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="21">
@@ -667,13 +661,13 @@
         <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>79.0</v>
+        <v>85.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>56.0</v>
+        <v>50.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="22">
@@ -687,7 +681,7 @@
         <v>50.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="23">
@@ -701,7 +695,7 @@
         <v>50.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>8.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="24">
@@ -729,7 +723,7 @@
         <v>50.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="26">
@@ -743,7 +737,7 @@
         <v>50.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="27">
@@ -757,7 +751,7 @@
         <v>50.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>0.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="28">
@@ -785,7 +779,7 @@
         <v>50.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>72.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="30">
@@ -799,7 +793,7 @@
         <v>50.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>1.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="31">
@@ -807,13 +801,13 @@
         <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>85.0</v>
+        <v>90.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>50.0</v>
+        <v>45.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="32">
@@ -821,13 +815,13 @@
         <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>85.0</v>
+        <v>90.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>50.0</v>
+        <v>45.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>29.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="33">
@@ -841,7 +835,7 @@
         <v>45.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>10.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="34">
@@ -849,13 +843,13 @@
         <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>90.0</v>
+        <v>93.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>45.0</v>
+        <v>42.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>2.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="35">
@@ -863,13 +857,13 @@
         <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>90.0</v>
+        <v>93.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>45.0</v>
+        <v>42.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>29.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="36">
@@ -883,7 +877,7 @@
         <v>42.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>40.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="37">
@@ -897,7 +891,7 @@
         <v>42.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>14.0</v>
+        <v>121.0</v>
       </c>
     </row>
     <row r="38">
@@ -905,13 +899,13 @@
         <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>42.0</v>
+        <v>41.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>85.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="39">
@@ -919,13 +913,13 @@
         <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>42.0</v>
+        <v>41.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>121.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="40">
@@ -939,7 +933,7 @@
         <v>41.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>9.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="41">
@@ -947,13 +941,13 @@
         <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>94.0</v>
+        <v>95.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>41.0</v>
+        <v>40.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>26.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="42">
@@ -961,13 +955,13 @@
         <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>94.0</v>
+        <v>95.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>41.0</v>
+        <v>40.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>67.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="43">
@@ -981,7 +975,7 @@
         <v>40.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>54.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="44">
@@ -995,7 +989,7 @@
         <v>40.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>25.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="45">
@@ -1003,13 +997,13 @@
         <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>95.0</v>
+        <v>101.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>40.0</v>
+        <v>34.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>23.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="46">
@@ -1017,13 +1011,13 @@
         <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>95.0</v>
+        <v>101.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>40.0</v>
+        <v>34.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>33.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="47">
@@ -1037,7 +1031,7 @@
         <v>34.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>3.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="48">
@@ -1051,7 +1045,7 @@
         <v>34.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="49">
@@ -1065,7 +1059,7 @@
         <v>34.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>44.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="50">
@@ -1079,7 +1073,7 @@
         <v>34.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="51">
@@ -1093,7 +1087,7 @@
         <v>34.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>0.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="52">
@@ -1101,13 +1095,13 @@
         <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>101.0</v>
+        <v>104.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>34.0</v>
+        <v>31.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="53">
@@ -1115,13 +1109,13 @@
         <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>101.0</v>
+        <v>104.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>34.0</v>
+        <v>31.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>58.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="54">
@@ -1135,7 +1129,7 @@
         <v>31.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="55">
@@ -1143,13 +1137,13 @@
         <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>104.0</v>
+        <v>106.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="56">
@@ -1157,13 +1151,13 @@
         <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>104.0</v>
+        <v>106.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="57">
@@ -1177,7 +1171,7 @@
         <v>29.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="58">
@@ -1191,7 +1185,7 @@
         <v>29.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="59">
@@ -1199,13 +1193,13 @@
         <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>106.0</v>
+        <v>110.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>29.0</v>
+        <v>25.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="60">
@@ -1213,10 +1207,10 @@
         <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>106.0</v>
+        <v>110.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>29.0</v>
+        <v>25.0</v>
       </c>
       <c r="D60" t="n" s="0">
         <v>0.0</v>
@@ -1241,13 +1235,13 @@
         <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>110.0</v>
+        <v>114.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>25.0</v>
+        <v>21.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="63">
@@ -1255,13 +1249,13 @@
         <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>110.0</v>
+        <v>114.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>25.0</v>
+        <v>21.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="64">
@@ -1275,7 +1269,7 @@
         <v>21.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="65">
@@ -1289,7 +1283,7 @@
         <v>21.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="66">
@@ -1297,13 +1291,13 @@
         <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>114.0</v>
+        <v>121.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>21.0</v>
+        <v>14.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="67">
@@ -1311,10 +1305,10 @@
         <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>114.0</v>
+        <v>121.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>21.0</v>
+        <v>14.0</v>
       </c>
       <c r="D67" t="n" s="0">
         <v>0.0</v>
@@ -1331,7 +1325,7 @@
         <v>14.0</v>
       </c>
       <c r="D68" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="69">
@@ -1339,13 +1333,13 @@
         <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>121.0</v>
+        <v>135.0</v>
       </c>
       <c r="C69" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="70">
@@ -1353,10 +1347,10 @@
         <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>121.0</v>
+        <v>135.0</v>
       </c>
       <c r="C70" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="D70" t="n" s="0">
         <v>0.0</v>
@@ -1373,7 +1367,7 @@
         <v>0.0</v>
       </c>
       <c r="D71" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="72">
@@ -1527,34 +1521,6 @@
         <v>0.0</v>
       </c>
       <c r="D82" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s" s="0">
-        <v>86</v>
-      </c>
-      <c r="B83" t="n" s="0">
-        <v>135.0</v>
-      </c>
-      <c r="C83" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D83" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s" s="0">
-        <v>87</v>
-      </c>
-      <c r="B84" t="n" s="0">
-        <v>135.0</v>
-      </c>
-      <c r="C84" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D84" t="n" s="0">
         <v>0.0</v>
       </c>
     </row>
@@ -1570,27 +1536,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="C1" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>89</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>90</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>91</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>92</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>93</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>94</v>
       </c>
       <c r="D2" t="n" s="0">
         <v>104.0</v>
@@ -1598,13 +1564,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>4.0</v>
@@ -1612,13 +1578,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>3.0</v>
@@ -1626,13 +1592,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>15.0</v>
@@ -1640,13 +1606,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B6" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="C6" t="s" s="0">
         <v>98</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>100</v>
       </c>
       <c r="D6" t="n" s="0">
         <v>9.0</v>
@@ -1664,16 +1630,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="C1" t="s" s="0">
         <v>88</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>89</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>90</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1688,18 +1654,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export-old/Coverage.xlsx
+++ b/gsc-export-old/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="107">
   <si>
     <t>Date</t>
   </si>
@@ -29,42 +29,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-12-06</t>
+    <t>2025-12-16</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2025-12-07</t>
-  </si>
-  <si>
-    <t>2025-12-08</t>
-  </si>
-  <si>
-    <t>2025-12-09</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>2025-12-11</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>2025-12-13</t>
-  </si>
-  <si>
-    <t>2025-12-14</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
-    <t>2025-12-16</t>
-  </si>
-  <si>
     <t>2025-12-17</t>
   </si>
   <si>
@@ -273,6 +243,48 @@
   </si>
   <si>
     <t>2026-02-24</t>
+  </si>
+  <si>
+    <t>2026-02-25</t>
+  </si>
+  <si>
+    <t>2026-02-26</t>
+  </si>
+  <si>
+    <t>2026-02-27</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>2026-03-02</t>
+  </si>
+  <si>
+    <t>2026-03-03</t>
+  </si>
+  <si>
+    <t>2026-03-04</t>
+  </si>
+  <si>
+    <t>2026-03-05</t>
+  </si>
+  <si>
+    <t>2026-03-06</t>
+  </si>
+  <si>
+    <t>2026-03-07</t>
+  </si>
+  <si>
+    <t>2026-03-08</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-03-10</t>
   </si>
   <si>
     <t>Reason</t>
@@ -373,7 +385,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -401,7 +413,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>2.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="3">
@@ -415,7 +427,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="4">
@@ -429,7 +441,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>3.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="5">
@@ -443,7 +455,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="6">
@@ -457,7 +469,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="7">
@@ -471,7 +483,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="8">
@@ -485,35 +497,35 @@
         <v>5</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="B9" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C9" t="s" s="0">
-        <v>5</v>
+      <c r="B9" t="n" s="0">
+        <v>79.0</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>56.0</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="B10" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C10" t="s" s="0">
-        <v>5</v>
+      <c r="B10" t="n" s="0">
+        <v>85.0</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>50.0</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>16.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="11">
@@ -521,13 +533,13 @@
         <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>73.0</v>
+        <v>85.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>62.0</v>
+        <v>50.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="12">
@@ -535,13 +547,13 @@
         <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>79.0</v>
+        <v>85.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>56.0</v>
+        <v>50.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="13">
@@ -549,13 +561,13 @@
         <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>79.0</v>
+        <v>85.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>56.0</v>
+        <v>50.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="14">
@@ -563,13 +575,13 @@
         <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>79.0</v>
+        <v>85.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>56.0</v>
+        <v>50.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>15.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="15">
@@ -577,13 +589,13 @@
         <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>79.0</v>
+        <v>85.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>56.0</v>
+        <v>50.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>7.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="16">
@@ -591,13 +603,13 @@
         <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>79.0</v>
+        <v>85.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>56.0</v>
+        <v>50.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="17">
@@ -605,13 +617,13 @@
         <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>79.0</v>
+        <v>85.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>56.0</v>
+        <v>50.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>3.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="18">
@@ -619,13 +631,13 @@
         <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>79.0</v>
+        <v>85.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>56.0</v>
+        <v>50.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="19">
@@ -633,10 +645,10 @@
         <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>79.0</v>
+        <v>85.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>56.0</v>
+        <v>50.0</v>
       </c>
       <c r="D19" t="n" s="0">
         <v>2.0</v>
@@ -653,7 +665,7 @@
         <v>50.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>1.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="21">
@@ -661,13 +673,13 @@
         <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>85.0</v>
+        <v>90.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>50.0</v>
+        <v>45.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="22">
@@ -675,10 +687,10 @@
         <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>85.0</v>
+        <v>90.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>50.0</v>
+        <v>45.0</v>
       </c>
       <c r="D22" t="n" s="0">
         <v>2.0</v>
@@ -689,13 +701,13 @@
         <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>85.0</v>
+        <v>90.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>50.0</v>
+        <v>45.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>2.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="24">
@@ -703,13 +715,13 @@
         <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>85.0</v>
+        <v>93.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>50.0</v>
+        <v>42.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>2.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="25">
@@ -717,13 +729,13 @@
         <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>85.0</v>
+        <v>93.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>50.0</v>
+        <v>42.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>0.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="26">
@@ -731,13 +743,13 @@
         <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
+        <v>93.0</v>
+      </c>
+      <c r="C26" t="n" s="0">
+        <v>42.0</v>
+      </c>
+      <c r="D26" t="n" s="0">
         <v>85.0</v>
-      </c>
-      <c r="C26" t="n" s="0">
-        <v>50.0</v>
-      </c>
-      <c r="D26" t="n" s="0">
-        <v>1.0</v>
       </c>
     </row>
     <row r="27">
@@ -745,13 +757,13 @@
         <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>85.0</v>
+        <v>93.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>50.0</v>
+        <v>42.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>72.0</v>
+        <v>121.0</v>
       </c>
     </row>
     <row r="28">
@@ -759,13 +771,13 @@
         <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>85.0</v>
+        <v>94.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>50.0</v>
+        <v>41.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="29">
@@ -773,13 +785,13 @@
         <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>85.0</v>
+        <v>94.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>50.0</v>
+        <v>41.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>2.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="30">
@@ -787,13 +799,13 @@
         <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>85.0</v>
+        <v>94.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>50.0</v>
+        <v>41.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>29.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="31">
@@ -801,13 +813,13 @@
         <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>90.0</v>
+        <v>95.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>45.0</v>
+        <v>40.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>10.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="32">
@@ -815,13 +827,13 @@
         <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>90.0</v>
+        <v>95.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>45.0</v>
+        <v>40.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>2.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="33">
@@ -829,13 +841,13 @@
         <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>90.0</v>
+        <v>95.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>45.0</v>
+        <v>40.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>29.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="34">
@@ -843,13 +855,13 @@
         <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>93.0</v>
+        <v>95.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>42.0</v>
+        <v>40.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>40.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="35">
@@ -857,13 +869,13 @@
         <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>93.0</v>
+        <v>101.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>42.0</v>
+        <v>34.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>14.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="36">
@@ -871,13 +883,13 @@
         <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>93.0</v>
+        <v>101.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>42.0</v>
+        <v>34.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>85.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="37">
@@ -885,13 +897,13 @@
         <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>93.0</v>
+        <v>101.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>42.0</v>
+        <v>34.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>121.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="38">
@@ -899,13 +911,13 @@
         <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>94.0</v>
+        <v>101.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>41.0</v>
+        <v>34.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="39">
@@ -913,13 +925,13 @@
         <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>94.0</v>
+        <v>101.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>41.0</v>
+        <v>34.0</v>
       </c>
       <c r="D39" t="n" s="0">
-        <v>26.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="40">
@@ -927,13 +939,13 @@
         <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>94.0</v>
+        <v>101.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>41.0</v>
+        <v>34.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>67.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="41">
@@ -941,13 +953,13 @@
         <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>95.0</v>
+        <v>101.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>40.0</v>
+        <v>34.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>54.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="42">
@@ -955,13 +967,13 @@
         <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>95.0</v>
+        <v>104.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>40.0</v>
+        <v>31.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>25.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="43">
@@ -969,13 +981,13 @@
         <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>95.0</v>
+        <v>104.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>40.0</v>
+        <v>31.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>23.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="44">
@@ -983,13 +995,13 @@
         <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>95.0</v>
+        <v>104.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>40.0</v>
+        <v>31.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>33.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="45">
@@ -997,13 +1009,13 @@
         <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>101.0</v>
+        <v>106.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>34.0</v>
+        <v>29.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="46">
@@ -1011,13 +1023,13 @@
         <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>101.0</v>
+        <v>106.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>34.0</v>
+        <v>29.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>13.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="47">
@@ -1025,13 +1037,13 @@
         <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>101.0</v>
+        <v>106.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>34.0</v>
+        <v>29.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>44.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="48">
@@ -1039,10 +1051,10 @@
         <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>101.0</v>
+        <v>106.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>34.0</v>
+        <v>29.0</v>
       </c>
       <c r="D48" t="n" s="0">
         <v>0.0</v>
@@ -1053,10 +1065,10 @@
         <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>101.0</v>
+        <v>110.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>34.0</v>
+        <v>25.0</v>
       </c>
       <c r="D49" t="n" s="0">
         <v>0.0</v>
@@ -1067,13 +1079,13 @@
         <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>101.0</v>
+        <v>110.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>34.0</v>
+        <v>25.0</v>
       </c>
       <c r="D50" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="51">
@@ -1081,13 +1093,13 @@
         <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>101.0</v>
+        <v>110.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>34.0</v>
+        <v>25.0</v>
       </c>
       <c r="D51" t="n" s="0">
-        <v>58.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="52">
@@ -1095,13 +1107,13 @@
         <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>104.0</v>
+        <v>114.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>31.0</v>
+        <v>21.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="53">
@@ -1109,10 +1121,10 @@
         <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>104.0</v>
+        <v>114.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>31.0</v>
+        <v>21.0</v>
       </c>
       <c r="D53" t="n" s="0">
         <v>2.0</v>
@@ -1123,13 +1135,13 @@
         <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>104.0</v>
+        <v>114.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>31.0</v>
+        <v>21.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="55">
@@ -1137,10 +1149,10 @@
         <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>106.0</v>
+        <v>114.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>29.0</v>
+        <v>21.0</v>
       </c>
       <c r="D55" t="n" s="0">
         <v>0.0</v>
@@ -1151,13 +1163,13 @@
         <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>106.0</v>
+        <v>121.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>29.0</v>
+        <v>14.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="57">
@@ -1165,13 +1177,13 @@
         <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>106.0</v>
+        <v>121.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>29.0</v>
+        <v>14.0</v>
       </c>
       <c r="D57" t="n" s="0">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="58">
@@ -1179,10 +1191,10 @@
         <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>106.0</v>
+        <v>121.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>29.0</v>
+        <v>14.0</v>
       </c>
       <c r="D58" t="n" s="0">
         <v>0.0</v>
@@ -1193,13 +1205,13 @@
         <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>110.0</v>
+        <v>135.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="60">
@@ -1207,10 +1219,10 @@
         <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>110.0</v>
+        <v>135.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
       <c r="D60" t="n" s="0">
         <v>0.0</v>
@@ -1221,10 +1233,10 @@
         <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>110.0</v>
+        <v>135.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
       <c r="D61" t="n" s="0">
         <v>0.0</v>
@@ -1235,13 +1247,13 @@
         <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>114.0</v>
+        <v>135.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>21.0</v>
+        <v>0.0</v>
       </c>
       <c r="D62" t="n" s="0">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="63">
@@ -1249,13 +1261,13 @@
         <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>114.0</v>
+        <v>135.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>21.0</v>
+        <v>0.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="64">
@@ -1263,13 +1275,13 @@
         <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>114.0</v>
+        <v>135.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>21.0</v>
+        <v>0.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="65">
@@ -1277,10 +1289,10 @@
         <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>114.0</v>
+        <v>135.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>21.0</v>
+        <v>0.0</v>
       </c>
       <c r="D65" t="n" s="0">
         <v>0.0</v>
@@ -1291,13 +1303,13 @@
         <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>121.0</v>
+        <v>135.0</v>
       </c>
       <c r="C66" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="67">
@@ -1305,10 +1317,10 @@
         <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>121.0</v>
+        <v>135.0</v>
       </c>
       <c r="C67" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="D67" t="n" s="0">
         <v>0.0</v>
@@ -1319,10 +1331,10 @@
         <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>121.0</v>
+        <v>135.0</v>
       </c>
       <c r="C68" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="D68" t="n" s="0">
         <v>0.0</v>
@@ -1339,7 +1351,7 @@
         <v>0.0</v>
       </c>
       <c r="D69" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="70">
@@ -1389,10 +1401,10 @@
         <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>135.0</v>
+        <v>134.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D73" t="n" s="0">
         <v>0.0</v>
@@ -1403,13 +1415,13 @@
         <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>135.0</v>
+        <v>134.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="75">
@@ -1417,13 +1429,13 @@
         <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>135.0</v>
+        <v>134.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="76">
@@ -1431,10 +1443,10 @@
         <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>135.0</v>
+        <v>134.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D76" t="n" s="0">
         <v>0.0</v>
@@ -1445,10 +1457,10 @@
         <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>135.0</v>
+        <v>134.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D77" t="n" s="0">
         <v>0.0</v>
@@ -1459,10 +1471,10 @@
         <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>135.0</v>
+        <v>134.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D78" t="n" s="0">
         <v>0.0</v>
@@ -1473,13 +1485,13 @@
         <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>135.0</v>
+        <v>134.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="80">
@@ -1487,10 +1499,10 @@
         <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>135.0</v>
+        <v>134.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D80" t="n" s="0">
         <v>0.0</v>
@@ -1501,13 +1513,13 @@
         <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>135.0</v>
+        <v>134.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D81" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="82">
@@ -1515,13 +1527,69 @@
         <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>135.0</v>
+        <v>134.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D82" t="n" s="0">
         <v>0.0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="B83" t="n" s="0">
+        <v>134.0</v>
+      </c>
+      <c r="C83" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="D83" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="B84" t="n" s="0">
+        <v>132.0</v>
+      </c>
+      <c r="C84" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="D84" t="n" s="0">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="B85" t="n" s="0">
+        <v>132.0</v>
+      </c>
+      <c r="C85" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="D85" t="n" s="0">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B86" t="n" s="0">
+        <v>132.0</v>
+      </c>
+      <c r="C86" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="D86" t="n" s="0">
+        <v>2.0</v>
       </c>
     </row>
   </sheetData>
@@ -1536,55 +1604,55 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>104.0</v>
+        <v>103.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D4" t="n" s="0">
         <v>3.0</v>
@@ -1592,30 +1660,30 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="C5" t="s" s="0">
         <v>96</v>
       </c>
-      <c r="C5" t="s" s="0">
-        <v>92</v>
-      </c>
       <c r="D5" t="n" s="0">
-        <v>15.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
     </row>
   </sheetData>
@@ -1630,16 +1698,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1654,18 +1722,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export-old/Coverage.xlsx
+++ b/gsc-export-old/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="111">
   <si>
     <t>Date</t>
   </si>
@@ -29,72 +29,6 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2025-12-16</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>2025-12-17</t>
-  </si>
-  <si>
-    <t>2025-12-18</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2025-12-20</t>
-  </si>
-  <si>
-    <t>2025-12-21</t>
-  </si>
-  <si>
-    <t>2025-12-22</t>
-  </si>
-  <si>
-    <t>2025-12-23</t>
-  </si>
-  <si>
-    <t>2025-12-24</t>
-  </si>
-  <si>
-    <t>2025-12-25</t>
-  </si>
-  <si>
-    <t>2025-12-26</t>
-  </si>
-  <si>
-    <t>2025-12-27</t>
-  </si>
-  <si>
-    <t>2025-12-28</t>
-  </si>
-  <si>
-    <t>2025-12-29</t>
-  </si>
-  <si>
-    <t>2025-12-30</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>2026-01-01</t>
-  </si>
-  <si>
-    <t>2026-01-02</t>
-  </si>
-  <si>
-    <t>2026-01-03</t>
-  </si>
-  <si>
-    <t>2026-01-04</t>
-  </si>
-  <si>
-    <t>2026-01-05</t>
-  </si>
-  <si>
     <t>2026-01-06</t>
   </si>
   <si>
@@ -287,6 +221,81 @@
     <t>2026-03-10</t>
   </si>
   <si>
+    <t>2026-03-11</t>
+  </si>
+  <si>
+    <t>2026-03-12</t>
+  </si>
+  <si>
+    <t>2026-03-13</t>
+  </si>
+  <si>
+    <t>2026-03-14</t>
+  </si>
+  <si>
+    <t>2026-03-15</t>
+  </si>
+  <si>
+    <t>2026-03-16</t>
+  </si>
+  <si>
+    <t>2026-03-17</t>
+  </si>
+  <si>
+    <t>2026-03-18</t>
+  </si>
+  <si>
+    <t>2026-03-19</t>
+  </si>
+  <si>
+    <t>2026-03-20</t>
+  </si>
+  <si>
+    <t>2026-03-21</t>
+  </si>
+  <si>
+    <t>2026-03-22</t>
+  </si>
+  <si>
+    <t>2026-03-23</t>
+  </si>
+  <si>
+    <t>2026-03-24</t>
+  </si>
+  <si>
+    <t>2026-03-25</t>
+  </si>
+  <si>
+    <t>2026-03-26</t>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2026-03-28</t>
+  </si>
+  <si>
+    <t>2026-03-29</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-03-31</t>
+  </si>
+  <si>
+    <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <t>2026-04-04</t>
+  </si>
+  <si>
     <t>Reason</t>
   </si>
   <si>
@@ -311,13 +320,16 @@
     <t>Not found (404)</t>
   </si>
   <si>
+    <t>Crawled - currently not indexed</t>
+  </si>
+  <si>
+    <t>Google systems</t>
+  </si>
+  <si>
     <t>Redirect error</t>
   </si>
   <si>
-    <t>Crawled - currently not indexed</t>
-  </si>
-  <si>
-    <t>Google systems</t>
+    <t>N/A</t>
   </si>
   <si>
     <t>Duplicate, Google chose different canonical than user</t>
@@ -385,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -406,291 +418,291 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>5</v>
+      <c r="B2" t="n" s="0">
+        <v>90.0</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>45.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>9.0</v>
+        <v>29.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="C3" t="s" s="0">
-        <v>5</v>
+      <c r="B3" t="n" s="0">
+        <v>93.0</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>42.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>9.0</v>
+        <v>40.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="B4" t="n" s="0">
+        <v>93.0</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>42.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="B5" t="n" s="0">
+        <v>93.0</v>
+      </c>
+      <c r="C5" t="n" s="0">
+        <v>42.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>7.0</v>
+        <v>85.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="B6" t="n" s="0">
+        <v>93.0</v>
+      </c>
+      <c r="C6" t="n" s="0">
+        <v>42.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>7.0</v>
+        <v>121.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C7" t="s" s="0">
-        <v>5</v>
+        <v>9</v>
+      </c>
+      <c r="B7" t="n" s="0">
+        <v>94.0</v>
+      </c>
+      <c r="C7" t="n" s="0">
+        <v>41.0</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>3.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="B8" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C8" t="s" s="0">
-        <v>5</v>
+        <v>10</v>
+      </c>
+      <c r="B8" t="n" s="0">
+        <v>94.0</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>41.0</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>12.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>79.0</v>
+        <v>94.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>56.0</v>
+        <v>41.0</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>2.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>85.0</v>
+        <v>95.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>50.0</v>
+        <v>40.0</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>1.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>85.0</v>
+        <v>95.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>50.0</v>
+        <v>40.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>8.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>85.0</v>
+        <v>95.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>50.0</v>
+        <v>40.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>2.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>85.0</v>
+        <v>95.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>50.0</v>
+        <v>40.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>2.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>85.0</v>
+        <v>101.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>50.0</v>
+        <v>34.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>85.0</v>
+        <v>101.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>50.0</v>
+        <v>34.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>85.0</v>
+        <v>101.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>50.0</v>
+        <v>34.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>1.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>85.0</v>
+        <v>101.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>50.0</v>
+        <v>34.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>72.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>85.0</v>
+        <v>101.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>50.0</v>
+        <v>34.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>85.0</v>
+        <v>101.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>50.0</v>
+        <v>34.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>85.0</v>
+        <v>101.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>50.0</v>
+        <v>34.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>29.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>90.0</v>
+        <v>104.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>45.0</v>
+        <v>31.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>10.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>90.0</v>
+        <v>104.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>45.0</v>
+        <v>31.0</v>
       </c>
       <c r="D22" t="n" s="0">
         <v>2.0</v>
@@ -698,237 +710,237 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>90.0</v>
+        <v>104.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>45.0</v>
+        <v>31.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>29.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>93.0</v>
+        <v>106.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>42.0</v>
+        <v>29.0</v>
       </c>
       <c r="D24" t="n" s="0">
-        <v>40.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>93.0</v>
+        <v>106.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>42.0</v>
+        <v>29.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>93.0</v>
+        <v>106.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>42.0</v>
+        <v>29.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>85.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>93.0</v>
+        <v>106.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>42.0</v>
+        <v>29.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>121.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>94.0</v>
+        <v>110.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>41.0</v>
+        <v>25.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>94.0</v>
+        <v>110.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>41.0</v>
+        <v>25.0</v>
       </c>
       <c r="D29" t="n" s="0">
-        <v>26.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>94.0</v>
+        <v>110.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>41.0</v>
+        <v>25.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>67.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>95.0</v>
+        <v>114.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>40.0</v>
+        <v>21.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>54.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>95.0</v>
+        <v>114.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>40.0</v>
+        <v>21.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>25.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>95.0</v>
+        <v>114.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>40.0</v>
+        <v>21.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>23.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>95.0</v>
+        <v>114.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>40.0</v>
+        <v>21.0</v>
       </c>
       <c r="D34" t="n" s="0">
-        <v>33.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>101.0</v>
+        <v>121.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>34.0</v>
+        <v>14.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>101.0</v>
+        <v>121.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>34.0</v>
+        <v>14.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>101.0</v>
+        <v>121.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>34.0</v>
+        <v>14.0</v>
       </c>
       <c r="D37" t="n" s="0">
-        <v>44.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>101.0</v>
+        <v>135.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>34.0</v>
+        <v>0.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>101.0</v>
+        <v>135.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>34.0</v>
+        <v>0.0</v>
       </c>
       <c r="D39" t="n" s="0">
         <v>0.0</v>
@@ -936,83 +948,83 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>101.0</v>
+        <v>135.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>34.0</v>
+        <v>0.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>101.0</v>
+        <v>135.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>34.0</v>
+        <v>0.0</v>
       </c>
       <c r="D41" t="n" s="0">
-        <v>58.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>104.0</v>
+        <v>135.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>31.0</v>
+        <v>0.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>104.0</v>
+        <v>135.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>31.0</v>
+        <v>0.0</v>
       </c>
       <c r="D43" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>104.0</v>
+        <v>135.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>31.0</v>
+        <v>0.0</v>
       </c>
       <c r="D44" t="n" s="0">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>106.0</v>
+        <v>135.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>29.0</v>
+        <v>0.0</v>
       </c>
       <c r="D45" t="n" s="0">
         <v>0.0</v>
@@ -1020,41 +1032,41 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>106.0</v>
+        <v>135.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>29.0</v>
+        <v>0.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>106.0</v>
+        <v>135.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>29.0</v>
+        <v>0.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>106.0</v>
+        <v>135.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>29.0</v>
+        <v>0.0</v>
       </c>
       <c r="D48" t="n" s="0">
         <v>0.0</v>
@@ -1062,13 +1074,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>110.0</v>
+        <v>135.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
       <c r="D49" t="n" s="0">
         <v>0.0</v>
@@ -1076,13 +1088,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>110.0</v>
+        <v>135.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
       <c r="D50" t="n" s="0">
         <v>0.0</v>
@@ -1090,13 +1102,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>110.0</v>
+        <v>135.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
       <c r="D51" t="n" s="0">
         <v>0.0</v>
@@ -1104,55 +1116,55 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>114.0</v>
+        <v>134.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>21.0</v>
+        <v>1.0</v>
       </c>
       <c r="D52" t="n" s="0">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>114.0</v>
+        <v>134.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>21.0</v>
+        <v>1.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>114.0</v>
+        <v>134.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>21.0</v>
+        <v>1.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>114.0</v>
+        <v>134.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>21.0</v>
+        <v>1.0</v>
       </c>
       <c r="D55" t="n" s="0">
         <v>0.0</v>
@@ -1160,27 +1172,27 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>121.0</v>
+        <v>134.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>14.0</v>
+        <v>1.0</v>
       </c>
       <c r="D56" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>121.0</v>
+        <v>134.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>14.0</v>
+        <v>1.0</v>
       </c>
       <c r="D57" t="n" s="0">
         <v>0.0</v>
@@ -1188,55 +1200,55 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>121.0</v>
+        <v>134.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>14.0</v>
+        <v>1.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>135.0</v>
+        <v>134.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>135.0</v>
+        <v>134.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>135.0</v>
+        <v>134.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D61" t="n" s="0">
         <v>0.0</v>
@@ -1244,13 +1256,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>135.0</v>
+        <v>134.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D62" t="n" s="0">
         <v>0.0</v>
@@ -1258,66 +1270,66 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>135.0</v>
+        <v>132.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>135.0</v>
+        <v>132.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>135.0</v>
+        <v>132.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>135.0</v>
+        <v>132.0</v>
       </c>
       <c r="C66" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>135.0</v>
+        <v>132.0</v>
       </c>
       <c r="C67" t="n" s="0">
         <v>0.0</v>
@@ -1328,10 +1340,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>135.0</v>
+        <v>132.0</v>
       </c>
       <c r="C68" t="n" s="0">
         <v>0.0</v>
@@ -1342,10 +1354,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>135.0</v>
+        <v>132.0</v>
       </c>
       <c r="C69" t="n" s="0">
         <v>0.0</v>
@@ -1356,10 +1368,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>135.0</v>
+        <v>132.0</v>
       </c>
       <c r="C70" t="n" s="0">
         <v>0.0</v>
@@ -1370,10 +1382,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>135.0</v>
+        <v>132.0</v>
       </c>
       <c r="C71" t="n" s="0">
         <v>0.0</v>
@@ -1384,10 +1396,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>135.0</v>
+        <v>132.0</v>
       </c>
       <c r="C72" t="n" s="0">
         <v>0.0</v>
@@ -1398,13 +1410,13 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>134.0</v>
+        <v>132.0</v>
       </c>
       <c r="C73" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D73" t="n" s="0">
         <v>0.0</v>
@@ -1412,41 +1424,41 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>134.0</v>
+        <v>132.0</v>
       </c>
       <c r="C74" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D74" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>134.0</v>
+        <v>132.0</v>
       </c>
       <c r="C75" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D75" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>134.0</v>
+        <v>132.0</v>
       </c>
       <c r="C76" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D76" t="n" s="0">
         <v>0.0</v>
@@ -1454,13 +1466,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>134.0</v>
+        <v>132.0</v>
       </c>
       <c r="C77" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D77" t="n" s="0">
         <v>0.0</v>
@@ -1468,13 +1480,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>134.0</v>
+        <v>132.0</v>
       </c>
       <c r="C78" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D78" t="n" s="0">
         <v>0.0</v>
@@ -1482,27 +1494,27 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>134.0</v>
+        <v>132.0</v>
       </c>
       <c r="C79" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D79" t="n" s="0">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>134.0</v>
+        <v>131.0</v>
       </c>
       <c r="C80" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D80" t="n" s="0">
         <v>0.0</v>
@@ -1510,27 +1522,27 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>134.0</v>
+        <v>131.0</v>
       </c>
       <c r="C81" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D81" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>134.0</v>
+        <v>131.0</v>
       </c>
       <c r="C82" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D82" t="n" s="0">
         <v>0.0</v>
@@ -1538,13 +1550,13 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>134.0</v>
+        <v>131.0</v>
       </c>
       <c r="C83" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D83" t="n" s="0">
         <v>0.0</v>
@@ -1552,44 +1564,100 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>132.0</v>
+        <v>130.0</v>
       </c>
       <c r="C84" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D84" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>132.0</v>
+        <v>130.0</v>
       </c>
       <c r="C85" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D85" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="B86" t="n" s="0">
+        <v>130.0</v>
+      </c>
+      <c r="C86" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D86" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="0">
         <v>89</v>
       </c>
-      <c r="B86" t="n" s="0">
-        <v>132.0</v>
-      </c>
-      <c r="C86" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="D86" t="n" s="0">
-        <v>2.0</v>
+      <c r="B87" t="n" s="0">
+        <v>126.0</v>
+      </c>
+      <c r="C87" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D87" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B88" t="n" s="0">
+        <v>126.0</v>
+      </c>
+      <c r="C88" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D88" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B89" t="n" s="0">
+        <v>126.0</v>
+      </c>
+      <c r="C89" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D89" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B90" t="n" s="0">
+        <v>126.0</v>
+      </c>
+      <c r="C90" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D90" t="n" s="0">
+        <v>0.0</v>
       </c>
     </row>
   </sheetData>
@@ -1604,41 +1672,41 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>103.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>5.0</v>
@@ -1646,44 +1714,44 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>3.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
     </row>
   </sheetData>
@@ -1698,16 +1766,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1722,18 +1790,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export-old/Coverage.xlsx
+++ b/gsc-export-old/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="109">
   <si>
     <t>Date</t>
   </si>
@@ -29,24 +29,12 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-01-06</t>
-  </si>
-  <si>
-    <t>2026-01-07</t>
-  </si>
-  <si>
-    <t>2026-01-08</t>
-  </si>
-  <si>
-    <t>2026-01-09</t>
-  </si>
-  <si>
-    <t>2026-01-10</t>
-  </si>
-  <si>
     <t>2026-01-11</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>2026-01-12</t>
   </si>
   <si>
@@ -294,6 +282,12 @@
   </si>
   <si>
     <t>2026-04-04</t>
+  </si>
+  <si>
+    <t>2026-04-05</t>
+  </si>
+  <si>
+    <t>2026-04-06</t>
   </si>
   <si>
     <t>Reason</t>
@@ -397,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -418,173 +412,173 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="n" s="0">
-        <v>90.0</v>
-      </c>
-      <c r="C2" t="n" s="0">
-        <v>45.0</v>
+      <c r="B2" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>29.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="B3" t="n" s="0">
-        <v>93.0</v>
-      </c>
-      <c r="C3" t="n" s="0">
-        <v>42.0</v>
+      <c r="C3" t="s" s="0">
+        <v>5</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>40.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>42.0</v>
+        <v>41.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>14.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>93.0</v>
+        <v>95.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>42.0</v>
+        <v>40.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>85.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>93.0</v>
+        <v>95.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>42.0</v>
+        <v>40.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>121.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>94.0</v>
+        <v>95.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>41.0</v>
+        <v>40.0</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>9.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>94.0</v>
+        <v>95.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>41.0</v>
+        <v>40.0</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>26.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>94.0</v>
+        <v>101.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>41.0</v>
+        <v>34.0</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>67.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>95.0</v>
+        <v>101.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>40.0</v>
+        <v>34.0</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>54.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>95.0</v>
+        <v>101.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>40.0</v>
+        <v>34.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>25.0</v>
+        <v>44.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>95.0</v>
+        <v>101.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>40.0</v>
+        <v>34.0</v>
       </c>
       <c r="D12" t="n" s="0">
-        <v>23.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>95.0</v>
+        <v>101.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>40.0</v>
+        <v>34.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>33.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" t="n" s="0">
         <v>101.0</v>
@@ -593,12 +587,12 @@
         <v>34.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" t="n" s="0">
         <v>101.0</v>
@@ -607,130 +601,130 @@
         <v>34.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>13.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>101.0</v>
+        <v>104.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>34.0</v>
+        <v>31.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>44.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>101.0</v>
+        <v>104.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>34.0</v>
+        <v>31.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>101.0</v>
+        <v>104.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>34.0</v>
+        <v>31.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>101.0</v>
+        <v>106.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>34.0</v>
+        <v>29.0</v>
       </c>
       <c r="D19" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>101.0</v>
+        <v>106.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>34.0</v>
+        <v>29.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>58.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>104.0</v>
+        <v>106.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>104.0</v>
+        <v>106.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>31.0</v>
+        <v>29.0</v>
       </c>
       <c r="D22" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>104.0</v>
+        <v>110.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>31.0</v>
+        <v>25.0</v>
       </c>
       <c r="D23" t="n" s="0">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>106.0</v>
+        <v>110.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>29.0</v>
+        <v>25.0</v>
       </c>
       <c r="D24" t="n" s="0">
         <v>0.0</v>
@@ -738,27 +732,27 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>106.0</v>
+        <v>110.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>29.0</v>
+        <v>25.0</v>
       </c>
       <c r="D25" t="n" s="0">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>106.0</v>
+        <v>114.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>29.0</v>
+        <v>21.0</v>
       </c>
       <c r="D26" t="n" s="0">
         <v>6.0</v>
@@ -766,41 +760,41 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>106.0</v>
+        <v>114.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>29.0</v>
+        <v>21.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>110.0</v>
+        <v>114.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>25.0</v>
+        <v>21.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>110.0</v>
+        <v>114.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>25.0</v>
+        <v>21.0</v>
       </c>
       <c r="D29" t="n" s="0">
         <v>0.0</v>
@@ -808,69 +802,69 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>110.0</v>
+        <v>121.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>25.0</v>
+        <v>14.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>114.0</v>
+        <v>121.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>21.0</v>
+        <v>14.0</v>
       </c>
       <c r="D31" t="n" s="0">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>114.0</v>
+        <v>121.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>21.0</v>
+        <v>14.0</v>
       </c>
       <c r="D32" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B33" t="n" s="0">
-        <v>114.0</v>
+        <v>135.0</v>
       </c>
       <c r="C33" t="n" s="0">
-        <v>21.0</v>
+        <v>0.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>114.0</v>
+        <v>135.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>21.0</v>
+        <v>0.0</v>
       </c>
       <c r="D34" t="n" s="0">
         <v>0.0</v>
@@ -878,27 +872,27 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>121.0</v>
+        <v>135.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>121.0</v>
+        <v>135.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="D36" t="n" s="0">
         <v>0.0</v>
@@ -906,13 +900,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>121.0</v>
+        <v>135.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="D37" t="n" s="0">
         <v>0.0</v>
@@ -920,7 +914,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B38" t="n" s="0">
         <v>135.0</v>
@@ -929,12 +923,12 @@
         <v>0.0</v>
       </c>
       <c r="D38" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B39" t="n" s="0">
         <v>135.0</v>
@@ -948,7 +942,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40" t="n" s="0">
         <v>135.0</v>
@@ -962,7 +956,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B41" t="n" s="0">
         <v>135.0</v>
@@ -976,7 +970,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B42" t="n" s="0">
         <v>135.0</v>
@@ -990,7 +984,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B43" t="n" s="0">
         <v>135.0</v>
@@ -1004,7 +998,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B44" t="n" s="0">
         <v>135.0</v>
@@ -1018,7 +1012,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B45" t="n" s="0">
         <v>135.0</v>
@@ -1032,7 +1026,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B46" t="n" s="0">
         <v>135.0</v>
@@ -1046,13 +1040,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>135.0</v>
+        <v>134.0</v>
       </c>
       <c r="C47" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D47" t="n" s="0">
         <v>0.0</v>
@@ -1060,41 +1054,41 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>135.0</v>
+        <v>134.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D48" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>135.0</v>
+        <v>134.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>135.0</v>
+        <v>134.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D50" t="n" s="0">
         <v>0.0</v>
@@ -1102,13 +1096,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>135.0</v>
+        <v>134.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D51" t="n" s="0">
         <v>0.0</v>
@@ -1116,7 +1110,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B52" t="n" s="0">
         <v>134.0</v>
@@ -1130,7 +1124,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B53" t="n" s="0">
         <v>134.0</v>
@@ -1139,12 +1133,12 @@
         <v>1.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B54" t="n" s="0">
         <v>134.0</v>
@@ -1153,12 +1147,12 @@
         <v>1.0</v>
       </c>
       <c r="D54" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B55" t="n" s="0">
         <v>134.0</v>
@@ -1167,12 +1161,12 @@
         <v>1.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B56" t="n" s="0">
         <v>134.0</v>
@@ -1186,7 +1180,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B57" t="n" s="0">
         <v>134.0</v>
@@ -1200,69 +1194,69 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B58" t="n" s="0">
-        <v>134.0</v>
+        <v>132.0</v>
       </c>
       <c r="C58" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B59" t="n" s="0">
-        <v>134.0</v>
+        <v>132.0</v>
       </c>
       <c r="C59" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B60" t="n" s="0">
-        <v>134.0</v>
+        <v>132.0</v>
       </c>
       <c r="C60" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B61" t="n" s="0">
-        <v>134.0</v>
+        <v>132.0</v>
       </c>
       <c r="C61" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>134.0</v>
+        <v>132.0</v>
       </c>
       <c r="C62" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D62" t="n" s="0">
         <v>0.0</v>
@@ -1270,49 +1264,49 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B63" t="n" s="0">
         <v>132.0</v>
       </c>
       <c r="C63" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D63" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B64" t="n" s="0">
         <v>132.0</v>
       </c>
       <c r="C64" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D64" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B65" t="n" s="0">
         <v>132.0</v>
       </c>
       <c r="C65" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D65" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B66" t="n" s="0">
         <v>132.0</v>
@@ -1321,12 +1315,12 @@
         <v>0.0</v>
       </c>
       <c r="D66" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B67" t="n" s="0">
         <v>132.0</v>
@@ -1340,7 +1334,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B68" t="n" s="0">
         <v>132.0</v>
@@ -1354,7 +1348,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B69" t="n" s="0">
         <v>132.0</v>
@@ -1368,7 +1362,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B70" t="n" s="0">
         <v>132.0</v>
@@ -1382,7 +1376,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B71" t="n" s="0">
         <v>132.0</v>
@@ -1396,7 +1390,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B72" t="n" s="0">
         <v>132.0</v>
@@ -1410,7 +1404,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B73" t="n" s="0">
         <v>132.0</v>
@@ -1424,7 +1418,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B74" t="n" s="0">
         <v>132.0</v>
@@ -1438,10 +1432,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>132.0</v>
+        <v>131.0</v>
       </c>
       <c r="C75" t="n" s="0">
         <v>0.0</v>
@@ -1452,10 +1446,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>132.0</v>
+        <v>131.0</v>
       </c>
       <c r="C76" t="n" s="0">
         <v>0.0</v>
@@ -1466,10 +1460,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>132.0</v>
+        <v>131.0</v>
       </c>
       <c r="C77" t="n" s="0">
         <v>0.0</v>
@@ -1480,10 +1474,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>132.0</v>
+        <v>131.0</v>
       </c>
       <c r="C78" t="n" s="0">
         <v>0.0</v>
@@ -1494,10 +1488,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>132.0</v>
+        <v>130.0</v>
       </c>
       <c r="C79" t="n" s="0">
         <v>0.0</v>
@@ -1508,10 +1502,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>131.0</v>
+        <v>130.0</v>
       </c>
       <c r="C80" t="n" s="0">
         <v>0.0</v>
@@ -1522,10 +1516,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>131.0</v>
+        <v>130.0</v>
       </c>
       <c r="C81" t="n" s="0">
         <v>0.0</v>
@@ -1536,10 +1530,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>131.0</v>
+        <v>126.0</v>
       </c>
       <c r="C82" t="n" s="0">
         <v>0.0</v>
@@ -1550,10 +1544,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>131.0</v>
+        <v>126.0</v>
       </c>
       <c r="C83" t="n" s="0">
         <v>0.0</v>
@@ -1564,10 +1558,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>130.0</v>
+        <v>126.0</v>
       </c>
       <c r="C84" t="n" s="0">
         <v>0.0</v>
@@ -1578,10 +1572,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>130.0</v>
+        <v>126.0</v>
       </c>
       <c r="C85" t="n" s="0">
         <v>0.0</v>
@@ -1592,10 +1586,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>130.0</v>
+        <v>125.0</v>
       </c>
       <c r="C86" t="n" s="0">
         <v>0.0</v>
@@ -1606,57 +1600,15 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B87" t="n" s="0">
-        <v>126.0</v>
+        <v>125.0</v>
       </c>
       <c r="C87" t="n" s="0">
         <v>0.0</v>
       </c>
       <c r="D87" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s" s="0">
-        <v>90</v>
-      </c>
-      <c r="B88" t="n" s="0">
-        <v>126.0</v>
-      </c>
-      <c r="C88" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D88" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s" s="0">
-        <v>91</v>
-      </c>
-      <c r="B89" t="n" s="0">
-        <v>126.0</v>
-      </c>
-      <c r="C89" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D89" t="n" s="0">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s" s="0">
-        <v>92</v>
-      </c>
-      <c r="B90" t="n" s="0">
-        <v>126.0</v>
-      </c>
-      <c r="C90" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D90" t="n" s="0">
         <v>0.0</v>
       </c>
     </row>
@@ -1672,41 +1624,41 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C1" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>94</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>95</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>96</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>97</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>98</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>99</v>
-      </c>
       <c r="D2" t="n" s="0">
-        <v>86.0</v>
+        <v>83.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D3" t="n" s="0">
         <v>5.0</v>
@@ -1714,27 +1666,27 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C5" t="s" s="0">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D5" t="n" s="0">
         <v>0.0</v>
@@ -1742,16 +1694,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s" s="0">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
   </sheetData>
@@ -1766,16 +1718,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="C1" t="s" s="0">
         <v>93</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="D1" t="s" s="0">
         <v>94</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>95</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1790,18 +1742,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/gsc-export-old/Coverage.xlsx
+++ b/gsc-export-old/Coverage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="109">
   <si>
     <t>Date</t>
   </si>
@@ -29,48 +29,6 @@
     <t>Impressions</t>
   </si>
   <si>
-    <t>2026-01-11</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>2026-01-12</t>
-  </si>
-  <si>
-    <t>2026-01-13</t>
-  </si>
-  <si>
-    <t>2026-01-14</t>
-  </si>
-  <si>
-    <t>2026-01-15</t>
-  </si>
-  <si>
-    <t>2026-01-16</t>
-  </si>
-  <si>
-    <t>2026-01-17</t>
-  </si>
-  <si>
-    <t>2026-01-18</t>
-  </si>
-  <si>
-    <t>2026-01-19</t>
-  </si>
-  <si>
-    <t>2026-01-20</t>
-  </si>
-  <si>
-    <t>2026-01-21</t>
-  </si>
-  <si>
-    <t>2026-01-22</t>
-  </si>
-  <si>
-    <t>2026-01-23</t>
-  </si>
-  <si>
     <t>2026-01-24</t>
   </si>
   <si>
@@ -288,6 +246,48 @@
   </si>
   <si>
     <t>2026-04-06</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>2026-04-11</t>
+  </si>
+  <si>
+    <t>2026-04-12</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>2026-04-14</t>
+  </si>
+  <si>
+    <t>2026-04-15</t>
+  </si>
+  <si>
+    <t>2026-04-16</t>
+  </si>
+  <si>
+    <t>2026-04-17</t>
+  </si>
+  <si>
+    <t>2026-04-18</t>
+  </si>
+  <si>
+    <t>2026-04-19</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
   </si>
   <si>
     <t>Reason</t>
@@ -391,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -412,151 +412,151 @@
       <c r="A2" t="s" s="0">
         <v>4</v>
       </c>
-      <c r="B2" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>5</v>
+      <c r="B2" t="n" s="0">
+        <v>101.0</v>
+      </c>
+      <c r="C2" t="n" s="0">
+        <v>34.0</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>9.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="C3" t="s" s="0">
-        <v>5</v>
+      <c r="B3" t="n" s="0">
+        <v>104.0</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>31.0</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>26.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="n" s="0">
-        <v>94.0</v>
+        <v>104.0</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>41.0</v>
+        <v>31.0</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>67.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="n" s="0">
-        <v>95.0</v>
+        <v>104.0</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>40.0</v>
+        <v>31.0</v>
       </c>
       <c r="D5" t="n" s="0">
-        <v>54.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="n" s="0">
-        <v>95.0</v>
+        <v>106.0</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>40.0</v>
+        <v>29.0</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n" s="0">
-        <v>95.0</v>
+        <v>106.0</v>
       </c>
       <c r="C7" t="n" s="0">
-        <v>40.0</v>
+        <v>29.0</v>
       </c>
       <c r="D7" t="n" s="0">
-        <v>23.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="n" s="0">
-        <v>95.0</v>
+        <v>106.0</v>
       </c>
       <c r="C8" t="n" s="0">
-        <v>40.0</v>
+        <v>29.0</v>
       </c>
       <c r="D8" t="n" s="0">
-        <v>33.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="n" s="0">
-        <v>101.0</v>
+        <v>106.0</v>
       </c>
       <c r="C9" t="n" s="0">
-        <v>34.0</v>
+        <v>29.0</v>
       </c>
       <c r="D9" t="n" s="0">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="n" s="0">
-        <v>101.0</v>
+        <v>110.0</v>
       </c>
       <c r="C10" t="n" s="0">
-        <v>34.0</v>
+        <v>25.0</v>
       </c>
       <c r="D10" t="n" s="0">
-        <v>13.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="n" s="0">
-        <v>101.0</v>
+        <v>110.0</v>
       </c>
       <c r="C11" t="n" s="0">
-        <v>34.0</v>
+        <v>25.0</v>
       </c>
       <c r="D11" t="n" s="0">
-        <v>44.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" t="n" s="0">
-        <v>101.0</v>
+        <v>110.0</v>
       </c>
       <c r="C12" t="n" s="0">
-        <v>34.0</v>
+        <v>25.0</v>
       </c>
       <c r="D12" t="n" s="0">
         <v>0.0</v>
@@ -564,97 +564,97 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" t="n" s="0">
-        <v>101.0</v>
+        <v>114.0</v>
       </c>
       <c r="C13" t="n" s="0">
-        <v>34.0</v>
+        <v>21.0</v>
       </c>
       <c r="D13" t="n" s="0">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" t="n" s="0">
-        <v>101.0</v>
+        <v>114.0</v>
       </c>
       <c r="C14" t="n" s="0">
-        <v>34.0</v>
+        <v>21.0</v>
       </c>
       <c r="D14" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" t="n" s="0">
-        <v>101.0</v>
+        <v>114.0</v>
       </c>
       <c r="C15" t="n" s="0">
-        <v>34.0</v>
+        <v>21.0</v>
       </c>
       <c r="D15" t="n" s="0">
-        <v>58.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" t="n" s="0">
-        <v>104.0</v>
+        <v>114.0</v>
       </c>
       <c r="C16" t="n" s="0">
-        <v>31.0</v>
+        <v>21.0</v>
       </c>
       <c r="D16" t="n" s="0">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" t="n" s="0">
-        <v>104.0</v>
+        <v>121.0</v>
       </c>
       <c r="C17" t="n" s="0">
-        <v>31.0</v>
+        <v>14.0</v>
       </c>
       <c r="D17" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" t="n" s="0">
-        <v>104.0</v>
+        <v>121.0</v>
       </c>
       <c r="C18" t="n" s="0">
-        <v>31.0</v>
+        <v>14.0</v>
       </c>
       <c r="D18" t="n" s="0">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="0">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" t="n" s="0">
-        <v>106.0</v>
+        <v>121.0</v>
       </c>
       <c r="C19" t="n" s="0">
-        <v>29.0</v>
+        <v>14.0</v>
       </c>
       <c r="D19" t="n" s="0">
         <v>0.0</v>
@@ -662,41 +662,41 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="0">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" t="n" s="0">
-        <v>106.0</v>
+        <v>135.0</v>
       </c>
       <c r="C20" t="n" s="0">
-        <v>29.0</v>
+        <v>0.0</v>
       </c>
       <c r="D20" t="n" s="0">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="0">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" t="n" s="0">
-        <v>106.0</v>
+        <v>135.0</v>
       </c>
       <c r="C21" t="n" s="0">
-        <v>29.0</v>
+        <v>0.0</v>
       </c>
       <c r="D21" t="n" s="0">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="0">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" t="n" s="0">
-        <v>106.0</v>
+        <v>135.0</v>
       </c>
       <c r="C22" t="n" s="0">
-        <v>29.0</v>
+        <v>0.0</v>
       </c>
       <c r="D22" t="n" s="0">
         <v>0.0</v>
@@ -704,13 +704,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="0">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" t="n" s="0">
-        <v>110.0</v>
+        <v>135.0</v>
       </c>
       <c r="C23" t="n" s="0">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
       <c r="D23" t="n" s="0">
         <v>0.0</v>
@@ -718,13 +718,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="0">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24" t="n" s="0">
-        <v>110.0</v>
+        <v>135.0</v>
       </c>
       <c r="C24" t="n" s="0">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
       <c r="D24" t="n" s="0">
         <v>0.0</v>
@@ -732,13 +732,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="0">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" t="n" s="0">
-        <v>110.0</v>
+        <v>135.0</v>
       </c>
       <c r="C25" t="n" s="0">
-        <v>25.0</v>
+        <v>0.0</v>
       </c>
       <c r="D25" t="n" s="0">
         <v>0.0</v>
@@ -746,55 +746,55 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="0">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26" t="n" s="0">
-        <v>114.0</v>
+        <v>135.0</v>
       </c>
       <c r="C26" t="n" s="0">
-        <v>21.0</v>
+        <v>0.0</v>
       </c>
       <c r="D26" t="n" s="0">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="0">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" t="n" s="0">
-        <v>114.0</v>
+        <v>135.0</v>
       </c>
       <c r="C27" t="n" s="0">
-        <v>21.0</v>
+        <v>0.0</v>
       </c>
       <c r="D27" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28" t="n" s="0">
-        <v>114.0</v>
+        <v>135.0</v>
       </c>
       <c r="C28" t="n" s="0">
-        <v>21.0</v>
+        <v>0.0</v>
       </c>
       <c r="D28" t="n" s="0">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="0">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" t="n" s="0">
-        <v>114.0</v>
+        <v>135.0</v>
       </c>
       <c r="C29" t="n" s="0">
-        <v>21.0</v>
+        <v>0.0</v>
       </c>
       <c r="D29" t="n" s="0">
         <v>0.0</v>
@@ -802,27 +802,27 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="0">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" t="n" s="0">
-        <v>121.0</v>
+        <v>135.0</v>
       </c>
       <c r="C30" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="D30" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="0">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" t="n" s="0">
-        <v>121.0</v>
+        <v>135.0</v>
       </c>
       <c r="C31" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="D31" t="n" s="0">
         <v>0.0</v>
@@ -830,13 +830,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="0">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" t="n" s="0">
-        <v>121.0</v>
+        <v>135.0</v>
       </c>
       <c r="C32" t="n" s="0">
-        <v>14.0</v>
+        <v>0.0</v>
       </c>
       <c r="D32" t="n" s="0">
         <v>0.0</v>
@@ -844,7 +844,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="0">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" t="n" s="0">
         <v>135.0</v>
@@ -853,18 +853,18 @@
         <v>0.0</v>
       </c>
       <c r="D33" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="0">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B34" t="n" s="0">
-        <v>135.0</v>
+        <v>134.0</v>
       </c>
       <c r="C34" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D34" t="n" s="0">
         <v>0.0</v>
@@ -872,41 +872,41 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="0">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" t="n" s="0">
-        <v>135.0</v>
+        <v>134.0</v>
       </c>
       <c r="C35" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D35" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="0">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" t="n" s="0">
-        <v>135.0</v>
+        <v>134.0</v>
       </c>
       <c r="C36" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D36" t="n" s="0">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="0">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" t="n" s="0">
-        <v>135.0</v>
+        <v>134.0</v>
       </c>
       <c r="C37" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D37" t="n" s="0">
         <v>0.0</v>
@@ -914,13 +914,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" t="n" s="0">
-        <v>135.0</v>
+        <v>134.0</v>
       </c>
       <c r="C38" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D38" t="n" s="0">
         <v>0.0</v>
@@ -928,13 +928,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="0">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" t="n" s="0">
-        <v>135.0</v>
+        <v>134.0</v>
       </c>
       <c r="C39" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D39" t="n" s="0">
         <v>0.0</v>
@@ -942,27 +942,27 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="0">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40" t="n" s="0">
-        <v>135.0</v>
+        <v>134.0</v>
       </c>
       <c r="C40" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D40" t="n" s="0">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="0">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B41" t="n" s="0">
-        <v>135.0</v>
+        <v>134.0</v>
       </c>
       <c r="C41" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D41" t="n" s="0">
         <v>0.0</v>
@@ -970,27 +970,27 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="0">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" t="n" s="0">
-        <v>135.0</v>
+        <v>134.0</v>
       </c>
       <c r="C42" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D42" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="0">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B43" t="n" s="0">
-        <v>135.0</v>
+        <v>134.0</v>
       </c>
       <c r="C43" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D43" t="n" s="0">
         <v>0.0</v>
@@ -998,13 +998,13 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" t="n" s="0">
-        <v>135.0</v>
+        <v>134.0</v>
       </c>
       <c r="C44" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D44" t="n" s="0">
         <v>0.0</v>
@@ -1012,55 +1012,55 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="0">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B45" t="n" s="0">
-        <v>135.0</v>
+        <v>132.0</v>
       </c>
       <c r="C45" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D45" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="0">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B46" t="n" s="0">
-        <v>135.0</v>
+        <v>132.0</v>
       </c>
       <c r="C46" t="n" s="0">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="D46" t="n" s="0">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="0">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B47" t="n" s="0">
-        <v>134.0</v>
+        <v>132.0</v>
       </c>
       <c r="C47" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="D47" t="n" s="0">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="0">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B48" t="n" s="0">
-        <v>134.0</v>
+        <v>132.0</v>
       </c>
       <c r="C48" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D48" t="n" s="0">
         <v>1.0</v>
@@ -1068,27 +1068,27 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="0">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B49" t="n" s="0">
-        <v>134.0</v>
+        <v>132.0</v>
       </c>
       <c r="C49" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D49" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="0">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B50" t="n" s="0">
-        <v>134.0</v>
+        <v>132.0</v>
       </c>
       <c r="C50" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D50" t="n" s="0">
         <v>0.0</v>
@@ -1096,13 +1096,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="0">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B51" t="n" s="0">
-        <v>134.0</v>
+        <v>132.0</v>
       </c>
       <c r="C51" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D51" t="n" s="0">
         <v>0.0</v>
@@ -1110,13 +1110,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="0">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B52" t="n" s="0">
-        <v>134.0</v>
+        <v>132.0</v>
       </c>
       <c r="C52" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D52" t="n" s="0">
         <v>0.0</v>
@@ -1124,27 +1124,27 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="0">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B53" t="n" s="0">
-        <v>134.0</v>
+        <v>132.0</v>
       </c>
       <c r="C53" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D53" t="n" s="0">
-        <v>6.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="0">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B54" t="n" s="0">
-        <v>134.0</v>
+        <v>132.0</v>
       </c>
       <c r="C54" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D54" t="n" s="0">
         <v>0.0</v>
@@ -1152,27 +1152,27 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="0">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B55" t="n" s="0">
-        <v>134.0</v>
+        <v>132.0</v>
       </c>
       <c r="C55" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D55" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="0">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B56" t="n" s="0">
-        <v>134.0</v>
+        <v>132.0</v>
       </c>
       <c r="C56" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D56" t="n" s="0">
         <v>0.0</v>
@@ -1180,13 +1180,13 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="0">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B57" t="n" s="0">
-        <v>134.0</v>
+        <v>132.0</v>
       </c>
       <c r="C57" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D57" t="n" s="0">
         <v>0.0</v>
@@ -1194,49 +1194,49 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="0">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B58" t="n" s="0">
         <v>132.0</v>
       </c>
       <c r="C58" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D58" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="0">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B59" t="n" s="0">
         <v>132.0</v>
       </c>
       <c r="C59" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D59" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="0">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B60" t="n" s="0">
         <v>132.0</v>
       </c>
       <c r="C60" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D60" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="0">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B61" t="n" s="0">
         <v>132.0</v>
@@ -1245,15 +1245,15 @@
         <v>0.0</v>
       </c>
       <c r="D61" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="0">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B62" t="n" s="0">
-        <v>132.0</v>
+        <v>131.0</v>
       </c>
       <c r="C62" t="n" s="0">
         <v>0.0</v>
@@ -1264,10 +1264,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="0">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B63" t="n" s="0">
-        <v>132.0</v>
+        <v>131.0</v>
       </c>
       <c r="C63" t="n" s="0">
         <v>0.0</v>
@@ -1278,10 +1278,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="0">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B64" t="n" s="0">
-        <v>132.0</v>
+        <v>131.0</v>
       </c>
       <c r="C64" t="n" s="0">
         <v>0.0</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="0">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B65" t="n" s="0">
-        <v>132.0</v>
+        <v>131.0</v>
       </c>
       <c r="C65" t="n" s="0">
         <v>0.0</v>
@@ -1306,10 +1306,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="0">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B66" t="n" s="0">
-        <v>132.0</v>
+        <v>130.0</v>
       </c>
       <c r="C66" t="n" s="0">
         <v>0.0</v>
@@ -1320,10 +1320,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="0">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B67" t="n" s="0">
-        <v>132.0</v>
+        <v>130.0</v>
       </c>
       <c r="C67" t="n" s="0">
         <v>0.0</v>
@@ -1334,10 +1334,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="0">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B68" t="n" s="0">
-        <v>132.0</v>
+        <v>130.0</v>
       </c>
       <c r="C68" t="n" s="0">
         <v>0.0</v>
@@ -1348,10 +1348,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="0">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B69" t="n" s="0">
-        <v>132.0</v>
+        <v>126.0</v>
       </c>
       <c r="C69" t="n" s="0">
         <v>0.0</v>
@@ -1362,10 +1362,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="0">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B70" t="n" s="0">
-        <v>132.0</v>
+        <v>126.0</v>
       </c>
       <c r="C70" t="n" s="0">
         <v>0.0</v>
@@ -1376,10 +1376,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="0">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B71" t="n" s="0">
-        <v>132.0</v>
+        <v>126.0</v>
       </c>
       <c r="C71" t="n" s="0">
         <v>0.0</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="0">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B72" t="n" s="0">
-        <v>132.0</v>
+        <v>126.0</v>
       </c>
       <c r="C72" t="n" s="0">
         <v>0.0</v>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="0">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B73" t="n" s="0">
-        <v>132.0</v>
+        <v>125.0</v>
       </c>
       <c r="C73" t="n" s="0">
         <v>0.0</v>
@@ -1418,10 +1418,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="0">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B74" t="n" s="0">
-        <v>132.0</v>
+        <v>125.0</v>
       </c>
       <c r="C74" t="n" s="0">
         <v>0.0</v>
@@ -1432,10 +1432,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="0">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B75" t="n" s="0">
-        <v>131.0</v>
+        <v>124.0</v>
       </c>
       <c r="C75" t="n" s="0">
         <v>0.0</v>
@@ -1446,10 +1446,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="0">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B76" t="n" s="0">
-        <v>131.0</v>
+        <v>124.0</v>
       </c>
       <c r="C76" t="n" s="0">
         <v>0.0</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="0">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B77" t="n" s="0">
-        <v>131.0</v>
+        <v>124.0</v>
       </c>
       <c r="C77" t="n" s="0">
         <v>0.0</v>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="0">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B78" t="n" s="0">
-        <v>131.0</v>
+        <v>124.0</v>
       </c>
       <c r="C78" t="n" s="0">
         <v>0.0</v>
@@ -1488,10 +1488,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="0">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B79" t="n" s="0">
-        <v>130.0</v>
+        <v>124.0</v>
       </c>
       <c r="C79" t="n" s="0">
         <v>0.0</v>
@@ -1502,10 +1502,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="0">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B80" t="n" s="0">
-        <v>130.0</v>
+        <v>124.0</v>
       </c>
       <c r="C80" t="n" s="0">
         <v>0.0</v>
@@ -1516,10 +1516,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="0">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B81" t="n" s="0">
-        <v>130.0</v>
+        <v>124.0</v>
       </c>
       <c r="C81" t="n" s="0">
         <v>0.0</v>
@@ -1530,10 +1530,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="0">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B82" t="n" s="0">
-        <v>126.0</v>
+        <v>119.0</v>
       </c>
       <c r="C82" t="n" s="0">
         <v>0.0</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="0">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B83" t="n" s="0">
-        <v>126.0</v>
+        <v>119.0</v>
       </c>
       <c r="C83" t="n" s="0">
         <v>0.0</v>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="0">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B84" t="n" s="0">
-        <v>126.0</v>
+        <v>119.0</v>
       </c>
       <c r="C84" t="n" s="0">
         <v>0.0</v>
@@ -1572,10 +1572,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="0">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B85" t="n" s="0">
-        <v>126.0</v>
+        <v>119.0</v>
       </c>
       <c r="C85" t="n" s="0">
         <v>0.0</v>
@@ -1586,10 +1586,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="0">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B86" t="n" s="0">
-        <v>125.0</v>
+        <v>118.0</v>
       </c>
       <c r="C86" t="n" s="0">
         <v>0.0</v>
@@ -1600,15 +1600,29 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B87" t="n" s="0">
+        <v>118.0</v>
+      </c>
+      <c r="C87" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D87" t="n" s="0">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="0">
         <v>90</v>
       </c>
-      <c r="B87" t="n" s="0">
-        <v>125.0</v>
-      </c>
-      <c r="C87" t="n" s="0">
-        <v>0.0</v>
-      </c>
-      <c r="D87" t="n" s="0">
+      <c r="B88" t="n" s="0">
+        <v>118.0</v>
+      </c>
+      <c r="C88" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="D88" t="n" s="0">
         <v>0.0</v>
       </c>
     </row>
@@ -1647,7 +1661,7 @@
         <v>97</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>83.0</v>
+        <v>62.0</v>
       </c>
     </row>
     <row r="3">
@@ -1661,7 +1675,7 @@
         <v>97</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="4">
@@ -1675,7 +1689,7 @@
         <v>97</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>31.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="5">
@@ -1703,7 +1717,7 @@
         <v>104</v>
       </c>
       <c r="D6" t="n" s="0">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
   </sheetData>
